--- a/modules/laboratorio/muestra/plantilla/CSJ-DRDYCS-LAYS – R - 2- RESULTADOS ANALISIS DE AGUAS.xlsx
+++ b/modules/laboratorio/muestra/plantilla/CSJ-DRDYCS-LAYS – R - 2- RESULTADOS ANALISIS DE AGUAS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SISTEMAS\gestionTI2026\modules\laboratorio\muestra\plantilla\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89299642-FF17-45AB-8B78-924E004C3581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{616C11A5-40E9-41A1-90B2-A0215694A3A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
   <si>
     <t>PROYECTO ESPECIAL CHAVIMOCHIC</t>
   </si>
@@ -85,9 +85,6 @@
   </si>
   <si>
     <t>ANIMALES</t>
-  </si>
-  <si>
-    <t>FINALIDAD DEL ANÁLISIS</t>
   </si>
   <si>
     <t>FECHA DE TOMA DE MUESTRA</t>
@@ -175,18 +172,6 @@
     <t>CSJ-DRDYCS-LAYS – R - 2</t>
   </si>
   <si>
-    <t>Ms.C. Ing. Fiorella Gamarra Quipas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms.C.Mblgo.Rosa Anais Baca Ardiles </t>
-  </si>
-  <si>
-    <t>RESPONSABLE LABORATORIO AGUAS Y SUELOS PECH</t>
-  </si>
-  <si>
-    <t>CBP: 10659</t>
-  </si>
-  <si>
     <t>UNIDAD DE MEDIDA</t>
   </si>
   <si>
@@ -197,6 +182,15 @@
   </si>
   <si>
     <t>OTROS</t>
+  </si>
+  <si>
+    <t>TIPO DE FUENTE</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
 </sst>
 </file>
@@ -887,7 +881,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1009,10 +1003,190 @@
     <xf numFmtId="17" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1039,190 +1213,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1654,8 +1645,8 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
       <c r="D2" s="28" t="s">
         <v>0</v>
       </c>
@@ -1663,14 +1654,14 @@
       <c r="G2" s="30"/>
       <c r="H2" s="30"/>
       <c r="I2" s="30"/>
-      <c r="J2" s="110" t="s">
-        <v>38</v>
-      </c>
-      <c r="K2" s="102"/>
+      <c r="J2" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" s="41"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
       <c r="D3" s="28" t="s">
         <v>1</v>
       </c>
@@ -1678,12 +1669,12 @@
       <c r="G3" s="30"/>
       <c r="H3" s="30"/>
       <c r="I3" s="30"/>
-      <c r="J3" s="110"/>
-      <c r="K3" s="103"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="42"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
       <c r="D4" s="28" t="s">
         <v>2</v>
       </c>
@@ -1695,8 +1686,8 @@
       <c r="K4" s="30"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
       <c r="D5" s="28" t="s">
         <v>3</v>
       </c>
@@ -1709,32 +1700,32 @@
     </row>
     <row r="6" spans="2:13" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="2:13" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B7" s="104" t="s">
+      <c r="B7" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
-      <c r="F7" s="104"/>
-      <c r="G7" s="104"/>
-      <c r="H7" s="104"/>
-      <c r="I7" s="104"/>
-      <c r="J7" s="104"/>
-      <c r="K7" s="104"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="43"/>
+      <c r="K7" s="43"/>
     </row>
     <row r="8" spans="2:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="42"/>
-      <c r="K8" s="42"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
     </row>
     <row r="9" spans="2:13" ht="7.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E9" s="31"/>
@@ -1746,10 +1737,10 @@
       <c r="K9" s="31"/>
     </row>
     <row r="10" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="71" t="s">
+      <c r="B10" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="72"/>
+      <c r="C10" s="46"/>
       <c r="D10" s="1" t="s">
         <v>7</v>
       </c>
@@ -1769,40 +1760,40 @@
     </row>
     <row r="11" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D11" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" s="112"/>
-      <c r="F11" s="112"/>
+        <v>46</v>
+      </c>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
     </row>
     <row r="12" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="71" t="s">
+      <c r="B12" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="98"/>
-      <c r="D12" s="73"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="74"/>
-      <c r="I12" s="74"/>
-      <c r="J12" s="74"/>
-      <c r="K12" s="75"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="56"/>
+      <c r="J12" s="56"/>
+      <c r="K12" s="57"/>
     </row>
     <row r="13" spans="2:13" ht="4.1500000000000004" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="71" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="98"/>
-      <c r="D14" s="111" t="s">
+      <c r="B14" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="54"/>
+      <c r="D14" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="111"/>
+      <c r="E14" s="58"/>
       <c r="F14" s="18"/>
-      <c r="G14" s="111" t="s">
+      <c r="G14" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="H14" s="111"/>
+      <c r="H14" s="58"/>
       <c r="I14" s="3"/>
       <c r="J14" s="1" t="s">
         <v>14</v>
@@ -1813,19 +1804,19 @@
       <c r="F15" s="17"/>
     </row>
     <row r="16" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="105" t="s">
+      <c r="B16" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="106"/>
-      <c r="D16" s="107" t="s">
+      <c r="C16" s="48"/>
+      <c r="D16" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="108"/>
+      <c r="E16" s="50"/>
       <c r="F16" s="18"/>
-      <c r="G16" s="109" t="s">
+      <c r="G16" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="108"/>
+      <c r="H16" s="50"/>
       <c r="I16" s="18"/>
       <c r="J16" s="1" t="s">
         <v>18</v>
@@ -1837,332 +1828,332 @@
       <c r="M17" s="32"/>
     </row>
     <row r="18" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="71" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="98"/>
-      <c r="D18" s="99" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="74"/>
-      <c r="F18" s="74"/>
-      <c r="G18" s="74"/>
-      <c r="H18" s="74"/>
-      <c r="I18" s="74"/>
-      <c r="J18" s="74"/>
-      <c r="K18" s="75"/>
+      <c r="B18" s="45" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="54"/>
+      <c r="D18" s="60" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="56"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="56"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="56"/>
+      <c r="K18" s="57"/>
     </row>
     <row r="19" spans="2:13" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="71" t="s">
+      <c r="B20" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="54"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="98"/>
-      <c r="D20" s="100"/>
-      <c r="E20" s="74"/>
-      <c r="F20" s="91" t="s">
-        <v>21</v>
-      </c>
-      <c r="G20" s="91"/>
-      <c r="H20" s="91"/>
-      <c r="I20" s="91"/>
-      <c r="J20" s="101"/>
-      <c r="K20" s="74"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="63"/>
+      <c r="K20" s="56"/>
     </row>
     <row r="21" spans="2:13" ht="4.1500000000000004" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="22" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="71" t="s">
+      <c r="B22" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="46"/>
+      <c r="D22" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="72"/>
-      <c r="D22" s="19" t="s">
+      <c r="E22" s="55"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="57"/>
+      <c r="H22" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="E22" s="73"/>
-      <c r="F22" s="74"/>
-      <c r="G22" s="75"/>
-      <c r="H22" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="I22" s="74"/>
-      <c r="J22" s="74"/>
-      <c r="K22" s="74"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="56"/>
+      <c r="K22" s="56"/>
     </row>
     <row r="23" spans="2:13" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="2:13" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="76" t="s">
+      <c r="B24" s="64" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="65"/>
+      <c r="D24" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="77"/>
-      <c r="D24" s="82" t="s">
+      <c r="E24" s="73"/>
+      <c r="F24" s="74"/>
+      <c r="G24" s="73"/>
+      <c r="H24" s="74"/>
+      <c r="I24" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="E24" s="85"/>
-      <c r="F24" s="86"/>
-      <c r="G24" s="85"/>
-      <c r="H24" s="86"/>
-      <c r="I24" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="J24" s="88"/>
-      <c r="K24" s="89"/>
+      <c r="J24" s="76"/>
+      <c r="K24" s="77"/>
     </row>
     <row r="25" spans="2:13" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="78"/>
-      <c r="C25" s="79"/>
-      <c r="D25" s="83"/>
-      <c r="E25" s="96"/>
-      <c r="F25" s="97"/>
-      <c r="G25" s="96"/>
-      <c r="H25" s="97"/>
-      <c r="I25" s="90"/>
-      <c r="J25" s="91"/>
-      <c r="K25" s="92"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="83"/>
+      <c r="F25" s="84"/>
+      <c r="G25" s="83"/>
+      <c r="H25" s="84"/>
+      <c r="I25" s="78"/>
+      <c r="J25" s="62"/>
+      <c r="K25" s="79"/>
     </row>
     <row r="26" spans="2:13" ht="22.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="80"/>
-      <c r="C26" s="81"/>
-      <c r="D26" s="84"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="69"/>
+      <c r="D26" s="72"/>
       <c r="E26" s="4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="I26" s="93"/>
-      <c r="J26" s="94"/>
-      <c r="K26" s="95"/>
+        <v>44</v>
+      </c>
+      <c r="I26" s="80"/>
+      <c r="J26" s="81"/>
+      <c r="K26" s="82"/>
     </row>
     <row r="27" spans="2:13" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="28" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="64" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" s="65"/>
+      <c r="B28" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="86"/>
       <c r="D28" s="33"/>
-      <c r="E28" s="66"/>
-      <c r="F28" s="66"/>
-      <c r="G28" s="66"/>
-      <c r="H28" s="66"/>
-      <c r="I28" s="66"/>
-      <c r="J28" s="66"/>
-      <c r="K28" s="67"/>
+      <c r="E28" s="87"/>
+      <c r="F28" s="87"/>
+      <c r="G28" s="87"/>
+      <c r="H28" s="87"/>
+      <c r="I28" s="87"/>
+      <c r="J28" s="87"/>
+      <c r="K28" s="88"/>
     </row>
     <row r="29" spans="2:13" ht="0.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B30" s="53"/>
-      <c r="C30" s="53"/>
+      <c r="B30" s="89"/>
+      <c r="C30" s="89"/>
       <c r="D30" s="36"/>
       <c r="E30" s="7"/>
       <c r="F30" s="8"/>
       <c r="G30" s="7"/>
       <c r="H30" s="8"/>
-      <c r="I30" s="53"/>
-      <c r="J30" s="53"/>
-      <c r="K30" s="53"/>
+      <c r="I30" s="89"/>
+      <c r="J30" s="89"/>
+      <c r="K30" s="89"/>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B31" s="53"/>
-      <c r="C31" s="53"/>
+      <c r="B31" s="89"/>
+      <c r="C31" s="89"/>
       <c r="D31" s="36"/>
       <c r="E31" s="9"/>
       <c r="F31" s="10"/>
       <c r="G31" s="11"/>
       <c r="H31" s="10"/>
-      <c r="I31" s="53"/>
-      <c r="J31" s="53"/>
-      <c r="K31" s="53"/>
+      <c r="I31" s="89"/>
+      <c r="J31" s="89"/>
+      <c r="K31" s="89"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B32" s="53"/>
-      <c r="C32" s="53"/>
+      <c r="B32" s="89"/>
+      <c r="C32" s="89"/>
       <c r="D32" s="36"/>
       <c r="E32" s="9"/>
       <c r="F32" s="10"/>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
-      <c r="I32" s="53"/>
-      <c r="J32" s="53"/>
-      <c r="K32" s="53"/>
+      <c r="I32" s="89"/>
+      <c r="J32" s="89"/>
+      <c r="K32" s="89"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B33" s="53"/>
-      <c r="C33" s="53"/>
+      <c r="B33" s="89"/>
+      <c r="C33" s="89"/>
       <c r="D33" s="36"/>
       <c r="E33" s="9"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="8"/>
-      <c r="I33" s="53"/>
-      <c r="J33" s="53"/>
-      <c r="K33" s="53"/>
+      <c r="I33" s="89"/>
+      <c r="J33" s="89"/>
+      <c r="K33" s="89"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B34" s="53"/>
-      <c r="C34" s="53"/>
+      <c r="B34" s="89"/>
+      <c r="C34" s="89"/>
       <c r="D34" s="38"/>
       <c r="E34" s="9"/>
       <c r="F34" s="8"/>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
-      <c r="I34" s="53"/>
-      <c r="J34" s="53"/>
-      <c r="K34" s="53"/>
+      <c r="I34" s="89"/>
+      <c r="J34" s="89"/>
+      <c r="K34" s="89"/>
     </row>
     <row r="35" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="41"/>
-      <c r="B35" s="41"/>
-      <c r="C35" s="41"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="41"/>
-      <c r="F35" s="41"/>
-      <c r="G35" s="41"/>
-      <c r="H35" s="41"/>
-      <c r="I35" s="41"/>
-      <c r="J35" s="41"/>
-      <c r="K35" s="41"/>
-      <c r="L35" s="41"/>
+      <c r="A35" s="52"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="52"/>
+      <c r="I35" s="52"/>
+      <c r="J35" s="52"/>
+      <c r="K35" s="52"/>
+      <c r="L35" s="52"/>
     </row>
     <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="64" t="s">
-        <v>30</v>
-      </c>
-      <c r="C36" s="65"/>
+      <c r="B36" s="85" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="86"/>
       <c r="D36" s="33"/>
-      <c r="E36" s="66"/>
-      <c r="F36" s="66"/>
-      <c r="G36" s="66"/>
-      <c r="H36" s="66"/>
-      <c r="I36" s="66"/>
-      <c r="J36" s="66"/>
-      <c r="K36" s="67"/>
+      <c r="E36" s="87"/>
+      <c r="F36" s="87"/>
+      <c r="G36" s="87"/>
+      <c r="H36" s="87"/>
+      <c r="I36" s="87"/>
+      <c r="J36" s="87"/>
+      <c r="K36" s="88"/>
     </row>
     <row r="37" spans="1:12" ht="1.1499999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="38" spans="1:12" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="69"/>
-      <c r="C38" s="70"/>
+      <c r="B38" s="90"/>
+      <c r="C38" s="91"/>
       <c r="D38" s="27"/>
       <c r="E38" s="22"/>
       <c r="F38" s="23"/>
       <c r="G38" s="24"/>
       <c r="H38" s="25"/>
-      <c r="I38" s="53"/>
-      <c r="J38" s="53"/>
-      <c r="K38" s="53"/>
+      <c r="I38" s="89"/>
+      <c r="J38" s="89"/>
+      <c r="K38" s="89"/>
     </row>
     <row r="39" spans="1:12" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="69"/>
-      <c r="C39" s="70"/>
+      <c r="B39" s="90"/>
+      <c r="C39" s="91"/>
       <c r="D39" s="27"/>
       <c r="E39" s="22"/>
       <c r="F39" s="23"/>
       <c r="G39" s="24"/>
       <c r="H39" s="25"/>
-      <c r="I39" s="53"/>
-      <c r="J39" s="53"/>
-      <c r="K39" s="53"/>
+      <c r="I39" s="89"/>
+      <c r="J39" s="89"/>
+      <c r="K39" s="89"/>
     </row>
     <row r="40" spans="1:12" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="68"/>
-      <c r="C40" s="68"/>
+      <c r="B40" s="92"/>
+      <c r="C40" s="92"/>
       <c r="D40" s="27"/>
       <c r="E40" s="22"/>
       <c r="F40" s="23"/>
       <c r="G40" s="24"/>
       <c r="H40" s="25"/>
-      <c r="I40" s="53"/>
-      <c r="J40" s="53"/>
-      <c r="K40" s="53"/>
+      <c r="I40" s="89"/>
+      <c r="J40" s="89"/>
+      <c r="K40" s="89"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B41" s="62"/>
-      <c r="C41" s="62"/>
+      <c r="B41" s="93"/>
+      <c r="C41" s="93"/>
       <c r="D41" s="27"/>
       <c r="E41" s="12"/>
       <c r="F41" s="14"/>
       <c r="G41" s="14"/>
       <c r="H41" s="14"/>
-      <c r="I41" s="53"/>
-      <c r="J41" s="53"/>
-      <c r="K41" s="53"/>
+      <c r="I41" s="89"/>
+      <c r="J41" s="89"/>
+      <c r="K41" s="89"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B42" s="62"/>
-      <c r="C42" s="62"/>
+      <c r="B42" s="93"/>
+      <c r="C42" s="93"/>
       <c r="D42" s="27"/>
       <c r="E42" s="12"/>
       <c r="F42" s="13"/>
       <c r="G42" s="14"/>
       <c r="H42" s="15"/>
-      <c r="I42" s="53"/>
-      <c r="J42" s="53"/>
-      <c r="K42" s="53"/>
+      <c r="I42" s="89"/>
+      <c r="J42" s="89"/>
+      <c r="K42" s="89"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B43" s="62"/>
-      <c r="C43" s="62"/>
+      <c r="B43" s="93"/>
+      <c r="C43" s="93"/>
       <c r="D43" s="27"/>
       <c r="E43" s="12"/>
       <c r="F43" s="13"/>
       <c r="G43" s="14"/>
       <c r="H43" s="15"/>
-      <c r="I43" s="53"/>
-      <c r="J43" s="53"/>
-      <c r="K43" s="53"/>
+      <c r="I43" s="89"/>
+      <c r="J43" s="89"/>
+      <c r="K43" s="89"/>
     </row>
     <row r="44" spans="1:12" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="68"/>
-      <c r="C44" s="68"/>
+      <c r="B44" s="92"/>
+      <c r="C44" s="92"/>
       <c r="D44" s="27"/>
       <c r="E44" s="22"/>
       <c r="F44" s="23"/>
       <c r="G44" s="24"/>
       <c r="H44" s="25"/>
-      <c r="I44" s="53"/>
-      <c r="J44" s="53"/>
-      <c r="K44" s="53"/>
+      <c r="I44" s="89"/>
+      <c r="J44" s="89"/>
+      <c r="K44" s="89"/>
     </row>
     <row r="45" spans="1:12" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="68"/>
-      <c r="C45" s="68"/>
+      <c r="B45" s="92"/>
+      <c r="C45" s="92"/>
       <c r="D45" s="27"/>
       <c r="E45" s="22"/>
       <c r="F45" s="23"/>
       <c r="G45" s="24"/>
       <c r="H45" s="25"/>
-      <c r="I45" s="53"/>
-      <c r="J45" s="53"/>
-      <c r="K45" s="53"/>
+      <c r="I45" s="89"/>
+      <c r="J45" s="89"/>
+      <c r="K45" s="89"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B46" s="62"/>
-      <c r="C46" s="62"/>
+      <c r="B46" s="93"/>
+      <c r="C46" s="93"/>
       <c r="D46" s="27"/>
       <c r="E46" s="12"/>
       <c r="F46" s="13"/>
       <c r="G46" s="14"/>
       <c r="H46" s="15"/>
-      <c r="I46" s="53"/>
-      <c r="J46" s="53"/>
-      <c r="K46" s="53"/>
+      <c r="I46" s="89"/>
+      <c r="J46" s="89"/>
+      <c r="K46" s="89"/>
     </row>
     <row r="47" spans="1:12" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="63"/>
-      <c r="C47" s="63"/>
+      <c r="B47" s="94"/>
+      <c r="C47" s="94"/>
       <c r="D47" s="27"/>
       <c r="E47" s="22"/>
       <c r="F47" s="23"/>
       <c r="G47" s="22"/>
       <c r="H47" s="37"/>
-      <c r="I47" s="53"/>
-      <c r="J47" s="53"/>
-      <c r="K47" s="53"/>
+      <c r="I47" s="89"/>
+      <c r="J47" s="89"/>
+      <c r="K47" s="89"/>
     </row>
     <row r="48" spans="1:12" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="17"/>
@@ -2170,121 +2161,121 @@
       <c r="D48" s="17"/>
     </row>
     <row r="49" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="64" t="s">
-        <v>31</v>
-      </c>
-      <c r="C49" s="65"/>
+      <c r="B49" s="85" t="s">
+        <v>30</v>
+      </c>
+      <c r="C49" s="86"/>
       <c r="D49" s="33"/>
-      <c r="E49" s="66"/>
-      <c r="F49" s="66"/>
-      <c r="G49" s="66"/>
-      <c r="H49" s="66"/>
-      <c r="I49" s="66"/>
-      <c r="J49" s="66"/>
-      <c r="K49" s="67"/>
+      <c r="E49" s="87"/>
+      <c r="F49" s="87"/>
+      <c r="G49" s="87"/>
+      <c r="H49" s="87"/>
+      <c r="I49" s="87"/>
+      <c r="J49" s="87"/>
+      <c r="K49" s="88"/>
     </row>
     <row r="50" spans="2:11" ht="2.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B51" s="53"/>
-      <c r="C51" s="53"/>
+      <c r="B51" s="89"/>
+      <c r="C51" s="89"/>
       <c r="D51" s="21"/>
       <c r="E51" s="9"/>
       <c r="F51" s="16"/>
-      <c r="G51" s="54"/>
-      <c r="H51" s="54"/>
-      <c r="I51" s="53"/>
-      <c r="J51" s="53"/>
-      <c r="K51" s="53"/>
+      <c r="G51" s="96"/>
+      <c r="H51" s="96"/>
+      <c r="I51" s="89"/>
+      <c r="J51" s="89"/>
+      <c r="K51" s="89"/>
     </row>
     <row r="52" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B52" s="55"/>
-      <c r="C52" s="56"/>
+      <c r="B52" s="101"/>
+      <c r="C52" s="102"/>
       <c r="D52" s="21"/>
       <c r="E52" s="9"/>
       <c r="F52" s="6"/>
-      <c r="G52" s="54"/>
-      <c r="H52" s="54"/>
-      <c r="I52" s="53"/>
-      <c r="J52" s="53"/>
-      <c r="K52" s="53"/>
+      <c r="G52" s="96"/>
+      <c r="H52" s="96"/>
+      <c r="I52" s="89"/>
+      <c r="J52" s="89"/>
+      <c r="K52" s="89"/>
     </row>
     <row r="53" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B53" s="57"/>
-      <c r="C53" s="57"/>
+      <c r="B53" s="95"/>
+      <c r="C53" s="95"/>
       <c r="D53" s="21"/>
       <c r="E53" s="9"/>
       <c r="F53" s="6"/>
-      <c r="G53" s="54"/>
-      <c r="H53" s="54"/>
-      <c r="I53" s="53"/>
-      <c r="J53" s="53"/>
-      <c r="K53" s="53"/>
+      <c r="G53" s="96"/>
+      <c r="H53" s="96"/>
+      <c r="I53" s="89"/>
+      <c r="J53" s="89"/>
+      <c r="K53" s="89"/>
     </row>
     <row r="54" spans="2:11" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E54" s="17"/>
       <c r="F54" s="17"/>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B55" s="58" t="s">
-        <v>32</v>
-      </c>
-      <c r="C55" s="59"/>
-      <c r="D55" s="59"/>
-      <c r="E55" s="59"/>
-      <c r="F55" s="59"/>
-      <c r="G55" s="59"/>
-      <c r="H55" s="59"/>
-      <c r="I55" s="59"/>
-      <c r="J55" s="59"/>
-      <c r="K55" s="60"/>
+      <c r="B55" s="97" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" s="98"/>
+      <c r="D55" s="98"/>
+      <c r="E55" s="98"/>
+      <c r="F55" s="98"/>
+      <c r="G55" s="98"/>
+      <c r="H55" s="98"/>
+      <c r="I55" s="98"/>
+      <c r="J55" s="98"/>
+      <c r="K55" s="99"/>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B56" s="45"/>
-      <c r="C56" s="46"/>
-      <c r="D56" s="46"/>
-      <c r="E56" s="46"/>
-      <c r="F56" s="46"/>
-      <c r="G56" s="46"/>
-      <c r="H56" s="46"/>
-      <c r="I56" s="46"/>
-      <c r="J56" s="46"/>
-      <c r="K56" s="47"/>
+      <c r="B56" s="105"/>
+      <c r="C56" s="106"/>
+      <c r="D56" s="106"/>
+      <c r="E56" s="106"/>
+      <c r="F56" s="106"/>
+      <c r="G56" s="106"/>
+      <c r="H56" s="106"/>
+      <c r="I56" s="106"/>
+      <c r="J56" s="106"/>
+      <c r="K56" s="107"/>
     </row>
     <row r="57" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="45"/>
-      <c r="C57" s="46"/>
-      <c r="D57" s="46"/>
-      <c r="E57" s="46"/>
-      <c r="F57" s="46"/>
-      <c r="G57" s="46"/>
-      <c r="H57" s="46"/>
-      <c r="I57" s="46"/>
-      <c r="J57" s="46"/>
-      <c r="K57" s="47"/>
+      <c r="B57" s="105"/>
+      <c r="C57" s="106"/>
+      <c r="D57" s="106"/>
+      <c r="E57" s="106"/>
+      <c r="F57" s="106"/>
+      <c r="G57" s="106"/>
+      <c r="H57" s="106"/>
+      <c r="I57" s="106"/>
+      <c r="J57" s="106"/>
+      <c r="K57" s="107"/>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B58" s="45"/>
-      <c r="C58" s="46"/>
-      <c r="D58" s="46"/>
-      <c r="E58" s="46"/>
-      <c r="F58" s="46"/>
-      <c r="G58" s="46"/>
-      <c r="H58" s="46"/>
-      <c r="I58" s="46"/>
-      <c r="J58" s="46"/>
-      <c r="K58" s="47"/>
+      <c r="B58" s="105"/>
+      <c r="C58" s="106"/>
+      <c r="D58" s="106"/>
+      <c r="E58" s="106"/>
+      <c r="F58" s="106"/>
+      <c r="G58" s="106"/>
+      <c r="H58" s="106"/>
+      <c r="I58" s="106"/>
+      <c r="J58" s="106"/>
+      <c r="K58" s="107"/>
     </row>
     <row r="59" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="48"/>
-      <c r="C59" s="49"/>
-      <c r="D59" s="49"/>
-      <c r="E59" s="49"/>
-      <c r="F59" s="49"/>
-      <c r="G59" s="49"/>
-      <c r="H59" s="49"/>
-      <c r="I59" s="49"/>
-      <c r="J59" s="49"/>
-      <c r="K59" s="50"/>
+      <c r="B59" s="108"/>
+      <c r="C59" s="109"/>
+      <c r="D59" s="109"/>
+      <c r="E59" s="109"/>
+      <c r="F59" s="109"/>
+      <c r="G59" s="109"/>
+      <c r="H59" s="109"/>
+      <c r="I59" s="109"/>
+      <c r="J59" s="109"/>
+      <c r="K59" s="110"/>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" s="34"/>
@@ -2299,36 +2290,36 @@
       <c r="K60" s="34"/>
     </row>
     <row r="61" spans="2:11" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="61" t="s">
+      <c r="B61" s="100" t="s">
+        <v>32</v>
+      </c>
+      <c r="C61" s="100"/>
+      <c r="D61" s="100"/>
+      <c r="E61" s="100"/>
+      <c r="F61" s="100"/>
+      <c r="G61" s="100"/>
+      <c r="H61" s="100"/>
+      <c r="I61" s="100"/>
+      <c r="J61" s="100"/>
+      <c r="K61" s="100"/>
+    </row>
+    <row r="62" spans="2:11" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="100" t="s">
         <v>33</v>
       </c>
-      <c r="C61" s="61"/>
-      <c r="D61" s="61"/>
-      <c r="E61" s="61"/>
-      <c r="F61" s="61"/>
-      <c r="G61" s="61"/>
-      <c r="H61" s="61"/>
-      <c r="I61" s="61"/>
-      <c r="J61" s="61"/>
-      <c r="K61" s="61"/>
-    </row>
-    <row r="62" spans="2:11" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="61" t="s">
-        <v>34</v>
-      </c>
-      <c r="C62" s="61"/>
-      <c r="D62" s="61"/>
-      <c r="E62" s="61"/>
-      <c r="F62" s="61"/>
-      <c r="G62" s="61"/>
-      <c r="H62" s="61"/>
-      <c r="I62" s="61"/>
-      <c r="J62" s="61"/>
-      <c r="K62" s="61"/>
+      <c r="C62" s="100"/>
+      <c r="D62" s="100"/>
+      <c r="E62" s="100"/>
+      <c r="F62" s="100"/>
+      <c r="G62" s="100"/>
+      <c r="H62" s="100"/>
+      <c r="I62" s="100"/>
+      <c r="J62" s="100"/>
+      <c r="K62" s="100"/>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" s="35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C63" s="35"/>
       <c r="D63" s="35"/>
@@ -2342,7 +2333,7 @@
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B64" s="35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C64" s="35"/>
       <c r="D64" s="35"/>
@@ -2355,116 +2346,185 @@
       <c r="K64" s="35"/>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B65" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="C65" s="44"/>
-      <c r="D65" s="44"/>
-      <c r="E65" s="44"/>
-      <c r="F65" s="44"/>
-      <c r="G65" s="44"/>
-      <c r="H65" s="44"/>
-      <c r="I65" s="44"/>
-      <c r="J65" s="44"/>
-      <c r="K65" s="44"/>
+      <c r="B65" s="104" t="s">
+        <v>36</v>
+      </c>
+      <c r="C65" s="104"/>
+      <c r="D65" s="104"/>
+      <c r="E65" s="104"/>
+      <c r="F65" s="104"/>
+      <c r="G65" s="104"/>
+      <c r="H65" s="104"/>
+      <c r="I65" s="104"/>
+      <c r="J65" s="104"/>
+      <c r="K65" s="104"/>
     </row>
     <row r="66" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="44"/>
-      <c r="C66" s="44"/>
-      <c r="D66" s="44"/>
-      <c r="E66" s="44"/>
-      <c r="F66" s="44"/>
-      <c r="G66" s="44"/>
-      <c r="H66" s="44"/>
-      <c r="I66" s="44"/>
-      <c r="J66" s="44"/>
-      <c r="K66" s="44"/>
+      <c r="B66" s="104"/>
+      <c r="C66" s="104"/>
+      <c r="D66" s="104"/>
+      <c r="E66" s="104"/>
+      <c r="F66" s="104"/>
+      <c r="G66" s="104"/>
+      <c r="H66" s="104"/>
+      <c r="I66" s="104"/>
+      <c r="J66" s="104"/>
+      <c r="K66" s="104"/>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H70" s="41"/>
-      <c r="I70" s="41"/>
-      <c r="J70" s="41"/>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D71" s="41"/>
-      <c r="E71" s="41"/>
-      <c r="F71" s="41"/>
+      <c r="H70" s="52"/>
+      <c r="I70" s="52"/>
+      <c r="J70" s="52"/>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D72" s="51"/>
-      <c r="E72" s="51"/>
-      <c r="F72" s="51"/>
-      <c r="H72" s="41"/>
-      <c r="I72" s="41"/>
-      <c r="J72" s="41"/>
+      <c r="D72" s="35"/>
+      <c r="E72" s="35"/>
+      <c r="F72" s="35"/>
+      <c r="H72" s="52"/>
+      <c r="I72" s="52"/>
+      <c r="J72" s="52"/>
     </row>
     <row r="73" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="52"/>
       <c r="C73" s="52"/>
       <c r="D73" s="52"/>
       <c r="E73" s="52"/>
-      <c r="G73" s="52"/>
-      <c r="H73" s="52"/>
-      <c r="I73" s="52"/>
-      <c r="J73" s="52"/>
+      <c r="G73" s="111"/>
+      <c r="H73" s="111"/>
+      <c r="I73" s="111"/>
+      <c r="J73" s="111"/>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B74" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="C74" s="41"/>
-      <c r="D74" s="41"/>
-      <c r="E74" s="41"/>
-      <c r="G74" s="41" t="s">
-        <v>45</v>
-      </c>
-      <c r="H74" s="41"/>
-      <c r="I74" s="41"/>
-      <c r="J74" s="41"/>
+      <c r="B74" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="C74" s="52"/>
+      <c r="D74" s="52"/>
+      <c r="E74" s="52"/>
+      <c r="G74" s="52" t="s">
+        <v>49</v>
+      </c>
+      <c r="H74" s="52"/>
+      <c r="I74" s="52"/>
+      <c r="J74" s="52"/>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B75" s="41" t="s">
-        <v>46</v>
-      </c>
-      <c r="C75" s="41"/>
-      <c r="D75" s="41"/>
-      <c r="E75" s="41"/>
-      <c r="G75" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="H75" s="41"/>
-      <c r="I75" s="41"/>
-      <c r="J75" s="41"/>
+      <c r="B75" s="52"/>
+      <c r="C75" s="52"/>
+      <c r="D75" s="52"/>
+      <c r="E75" s="52"/>
+      <c r="G75" s="52"/>
+      <c r="H75" s="52"/>
+      <c r="I75" s="52"/>
+      <c r="J75" s="52"/>
     </row>
     <row r="78" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A78" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="B78" s="42"/>
-      <c r="C78" s="42"/>
-      <c r="D78" s="42" t="s">
+      <c r="A78" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="B78" s="44"/>
+      <c r="C78" s="44"/>
+      <c r="D78" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="E78" s="44"/>
+      <c r="F78" s="44"/>
+      <c r="G78" s="44"/>
+      <c r="J78" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="E78" s="42"/>
-      <c r="F78" s="42"/>
-      <c r="G78" s="42"/>
-      <c r="J78" s="39" t="s">
+    </row>
+    <row r="79" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="D79" s="103" t="s">
+        <v>41</v>
+      </c>
+      <c r="E79" s="103"/>
+      <c r="F79" s="103"/>
+      <c r="G79" s="103"/>
+      <c r="J79" s="40" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="D79" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="E79" s="43"/>
-      <c r="F79" s="43"/>
-      <c r="G79" s="43"/>
-      <c r="J79" s="40" t="s">
-        <v>41</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="95">
+  <mergeCells count="93">
+    <mergeCell ref="D78:G78"/>
+    <mergeCell ref="D79:G79"/>
+    <mergeCell ref="A78:C78"/>
+    <mergeCell ref="B65:K66"/>
+    <mergeCell ref="B56:K59"/>
+    <mergeCell ref="H72:J72"/>
+    <mergeCell ref="H70:J70"/>
+    <mergeCell ref="B75:E75"/>
+    <mergeCell ref="G75:J75"/>
+    <mergeCell ref="B74:E74"/>
+    <mergeCell ref="G74:J74"/>
+    <mergeCell ref="B73:E73"/>
+    <mergeCell ref="G73:J73"/>
+    <mergeCell ref="B62:K62"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="I51:K51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="I52:K52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="I53:K53"/>
+    <mergeCell ref="B55:K55"/>
+    <mergeCell ref="B61:K61"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="I46:K46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="I47:K47"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="E49:K49"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="A35:L35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="E36:K36"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="E28:K28"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="B24:C26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I24:K26"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:K18"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="J20:K20"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="B7:K7"/>
     <mergeCell ref="B8:K8"/>
@@ -2480,86 +2540,6 @@
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="E11:F11"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:K18"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="B24:C26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="I24:K26"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="E28:K28"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="A35:L35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="E36:K36"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="I46:K46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="I47:K47"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="E49:K49"/>
-    <mergeCell ref="B74:E74"/>
-    <mergeCell ref="G74:J74"/>
-    <mergeCell ref="B73:E73"/>
-    <mergeCell ref="G73:J73"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="I51:K51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="G52:H52"/>
-    <mergeCell ref="I52:K52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="G53:H53"/>
-    <mergeCell ref="I53:K53"/>
-    <mergeCell ref="B55:K55"/>
-    <mergeCell ref="B61:K61"/>
-    <mergeCell ref="B62:K62"/>
-    <mergeCell ref="B65:K66"/>
-    <mergeCell ref="B56:K59"/>
-    <mergeCell ref="H72:J72"/>
-    <mergeCell ref="H70:J70"/>
-    <mergeCell ref="D72:F72"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="B75:E75"/>
-    <mergeCell ref="G75:J75"/>
-    <mergeCell ref="D78:G78"/>
-    <mergeCell ref="D79:G79"/>
-    <mergeCell ref="A78:C78"/>
   </mergeCells>
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.59055118110236227" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/modules/laboratorio/muestra/plantilla/CSJ-DRDYCS-LAYS – R - 2- RESULTADOS ANALISIS DE AGUAS.xlsx
+++ b/modules/laboratorio/muestra/plantilla/CSJ-DRDYCS-LAYS – R - 2- RESULTADOS ANALISIS DE AGUAS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SISTEMAS\gestionTI2026\modules\laboratorio\muestra\plantilla\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{616C11A5-40E9-41A1-90B2-A0215694A3A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA258392-F298-4D20-8882-E39FC123C2FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="9915" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FORMATO 002 -2024" sheetId="1" r:id="rId1"/>
@@ -357,7 +357,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="43">
+  <borders count="47">
     <border>
       <left/>
       <right/>
@@ -877,11 +877,55 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -943,9 +987,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1003,6 +1044,24 @@
     <xf numFmtId="17" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1135,18 +1194,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1156,6 +1203,12 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1165,6 +1218,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1213,8 +1269,8 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1629,118 +1685,118 @@
   <dimension ref="A2:M79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="29" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="29" customWidth="1"/>
-    <col min="3" max="3" width="19.85546875" style="29" customWidth="1"/>
-    <col min="4" max="4" width="19.5703125" style="29" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="29" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" style="29" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="29" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" style="29" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" style="29" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" style="29" customWidth="1"/>
-    <col min="11" max="11" width="10.42578125" style="29" customWidth="1"/>
-    <col min="12" max="12" width="3.85546875" style="29" customWidth="1"/>
-    <col min="13" max="16384" width="11.42578125" style="29"/>
+    <col min="1" max="1" width="3.42578125" style="28" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" style="28" customWidth="1"/>
+    <col min="4" max="4" width="19.5703125" style="28" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="28" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" style="28" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="28" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" style="28" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" style="28" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" style="28" customWidth="1"/>
+    <col min="11" max="11" width="10.42578125" style="28" customWidth="1"/>
+    <col min="12" max="12" width="3.85546875" style="28" customWidth="1"/>
+    <col min="13" max="16384" width="11.42578125" style="28"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="28" t="s">
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="53" t="s">
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="K2" s="41"/>
+      <c r="K2" s="46"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="28" t="s">
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="42"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="47"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="28" t="s">
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="28" t="s">
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
     </row>
     <row r="6" spans="2:13" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="2:13" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="43"/>
-      <c r="K7" s="43"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="48"/>
     </row>
     <row r="8" spans="2:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="44" t="s">
+      <c r="B8" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="49"/>
     </row>
     <row r="9" spans="2:13" ht="7.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="31"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
     </row>
     <row r="10" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="46"/>
+      <c r="C10" s="51"/>
       <c r="D10" s="1" t="s">
         <v>7</v>
       </c>
@@ -1759,41 +1815,41 @@
       <c r="K10" s="18"/>
     </row>
     <row r="11" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D11" s="31" t="s">
+      <c r="D11" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
     </row>
     <row r="12" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="54"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="56"/>
-      <c r="J12" s="56"/>
-      <c r="K12" s="57"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="62"/>
     </row>
     <row r="13" spans="2:13" ht="4.1500000000000004" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="54"/>
-      <c r="D14" s="58" t="s">
+      <c r="C14" s="59"/>
+      <c r="D14" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="58"/>
+      <c r="E14" s="63"/>
       <c r="F14" s="18"/>
-      <c r="G14" s="58" t="s">
+      <c r="G14" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="H14" s="58"/>
+      <c r="H14" s="63"/>
       <c r="I14" s="3"/>
       <c r="J14" s="1" t="s">
         <v>14</v>
@@ -1804,116 +1860,116 @@
       <c r="F15" s="17"/>
     </row>
     <row r="16" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="47" t="s">
+      <c r="B16" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="48"/>
-      <c r="D16" s="49" t="s">
+      <c r="C16" s="53"/>
+      <c r="D16" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="50"/>
+      <c r="E16" s="55"/>
       <c r="F16" s="18"/>
-      <c r="G16" s="51" t="s">
+      <c r="G16" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="50"/>
+      <c r="H16" s="55"/>
       <c r="I16" s="18"/>
       <c r="J16" s="1" t="s">
         <v>18</v>
       </c>
       <c r="K16" s="3"/>
-      <c r="M16" s="32"/>
+      <c r="M16" s="31"/>
     </row>
     <row r="17" spans="2:13" ht="3.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M17" s="32"/>
+      <c r="M17" s="31"/>
     </row>
     <row r="18" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="45" t="s">
+      <c r="B18" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="54"/>
-      <c r="D18" s="60" t="s">
+      <c r="C18" s="59"/>
+      <c r="D18" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="56"/>
-      <c r="F18" s="56"/>
-      <c r="G18" s="56"/>
-      <c r="H18" s="56"/>
-      <c r="I18" s="56"/>
-      <c r="J18" s="56"/>
-      <c r="K18" s="57"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="61"/>
+      <c r="K18" s="62"/>
     </row>
     <row r="19" spans="2:13" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="45" t="s">
+      <c r="B20" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="54"/>
-      <c r="D20" s="61"/>
-      <c r="E20" s="56"/>
-      <c r="F20" s="62" t="s">
+      <c r="C20" s="59"/>
+      <c r="D20" s="66"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="63"/>
-      <c r="K20" s="56"/>
+      <c r="G20" s="67"/>
+      <c r="H20" s="67"/>
+      <c r="I20" s="67"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="61"/>
     </row>
     <row r="21" spans="2:13" ht="4.1500000000000004" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="22" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="45" t="s">
+      <c r="B22" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="46"/>
+      <c r="C22" s="51"/>
       <c r="D22" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="55"/>
-      <c r="F22" s="56"/>
-      <c r="G22" s="57"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="61"/>
+      <c r="G22" s="62"/>
       <c r="H22" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="I22" s="56"/>
-      <c r="J22" s="56"/>
-      <c r="K22" s="56"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="61"/>
+      <c r="K22" s="61"/>
     </row>
     <row r="23" spans="2:13" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="2:13" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="64" t="s">
+      <c r="B24" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="65"/>
-      <c r="D24" s="70" t="s">
+      <c r="C24" s="70"/>
+      <c r="D24" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="E24" s="73"/>
-      <c r="F24" s="74"/>
-      <c r="G24" s="73"/>
-      <c r="H24" s="74"/>
-      <c r="I24" s="75" t="s">
+      <c r="E24" s="78"/>
+      <c r="F24" s="79"/>
+      <c r="G24" s="78"/>
+      <c r="H24" s="79"/>
+      <c r="I24" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="J24" s="76"/>
-      <c r="K24" s="77"/>
+      <c r="J24" s="81"/>
+      <c r="K24" s="82"/>
     </row>
     <row r="25" spans="2:13" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="66"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="71"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="84"/>
-      <c r="G25" s="83"/>
-      <c r="H25" s="84"/>
-      <c r="I25" s="78"/>
-      <c r="J25" s="62"/>
-      <c r="K25" s="79"/>
+      <c r="B25" s="71"/>
+      <c r="C25" s="72"/>
+      <c r="D25" s="76"/>
+      <c r="E25" s="88"/>
+      <c r="F25" s="89"/>
+      <c r="G25" s="88"/>
+      <c r="H25" s="89"/>
+      <c r="I25" s="83"/>
+      <c r="J25" s="67"/>
+      <c r="K25" s="84"/>
     </row>
     <row r="26" spans="2:13" ht="22.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="68"/>
-      <c r="C26" s="69"/>
-      <c r="D26" s="72"/>
+      <c r="B26" s="73"/>
+      <c r="C26" s="74"/>
+      <c r="D26" s="77"/>
       <c r="E26" s="4" t="s">
         <v>43</v>
       </c>
@@ -1926,527 +1982,526 @@
       <c r="H26" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I26" s="80"/>
-      <c r="J26" s="81"/>
-      <c r="K26" s="82"/>
+      <c r="I26" s="85"/>
+      <c r="J26" s="86"/>
+      <c r="K26" s="87"/>
     </row>
     <row r="27" spans="2:13" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="28" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="85" t="s">
+      <c r="B28" s="115" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="86"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="87"/>
-      <c r="F28" s="87"/>
-      <c r="G28" s="87"/>
-      <c r="H28" s="87"/>
-      <c r="I28" s="87"/>
-      <c r="J28" s="87"/>
-      <c r="K28" s="88"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="42"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="42"/>
+      <c r="K28" s="43"/>
     </row>
     <row r="29" spans="2:13" ht="0.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B30" s="89"/>
-      <c r="C30" s="89"/>
-      <c r="D30" s="36"/>
+      <c r="B30" s="90"/>
+      <c r="C30" s="90"/>
+      <c r="D30" s="35"/>
       <c r="E30" s="7"/>
       <c r="F30" s="8"/>
       <c r="G30" s="7"/>
       <c r="H30" s="8"/>
-      <c r="I30" s="89"/>
-      <c r="J30" s="89"/>
-      <c r="K30" s="89"/>
-    </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B31" s="89"/>
-      <c r="C31" s="89"/>
-      <c r="D31" s="36"/>
+      <c r="I30" s="90"/>
+      <c r="J30" s="90"/>
+      <c r="K30" s="90"/>
+    </row>
+    <row r="31" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="90"/>
+      <c r="C31" s="90"/>
+      <c r="D31" s="35"/>
       <c r="E31" s="9"/>
       <c r="F31" s="10"/>
       <c r="G31" s="11"/>
       <c r="H31" s="10"/>
-      <c r="I31" s="89"/>
-      <c r="J31" s="89"/>
-      <c r="K31" s="89"/>
-    </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B32" s="89"/>
-      <c r="C32" s="89"/>
-      <c r="D32" s="36"/>
+      <c r="I31" s="90"/>
+      <c r="J31" s="90"/>
+      <c r="K31" s="90"/>
+    </row>
+    <row r="32" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="90"/>
+      <c r="C32" s="90"/>
+      <c r="D32" s="35"/>
       <c r="E32" s="9"/>
       <c r="F32" s="10"/>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
-      <c r="I32" s="89"/>
-      <c r="J32" s="89"/>
-      <c r="K32" s="89"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B33" s="89"/>
-      <c r="C33" s="89"/>
-      <c r="D33" s="36"/>
+      <c r="I32" s="90"/>
+      <c r="J32" s="90"/>
+      <c r="K32" s="90"/>
+    </row>
+    <row r="33" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="90"/>
+      <c r="C33" s="90"/>
+      <c r="D33" s="35"/>
       <c r="E33" s="9"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="8"/>
-      <c r="I33" s="89"/>
-      <c r="J33" s="89"/>
-      <c r="K33" s="89"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B34" s="89"/>
-      <c r="C34" s="89"/>
-      <c r="D34" s="38"/>
+      <c r="I33" s="90"/>
+      <c r="J33" s="90"/>
+      <c r="K33" s="90"/>
+    </row>
+    <row r="34" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="90"/>
+      <c r="C34" s="90"/>
+      <c r="D34" s="37"/>
       <c r="E34" s="9"/>
       <c r="F34" s="8"/>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
-      <c r="I34" s="89"/>
-      <c r="J34" s="89"/>
-      <c r="K34" s="89"/>
-    </row>
-    <row r="35" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="52"/>
-      <c r="B35" s="52"/>
-      <c r="C35" s="52"/>
-      <c r="D35" s="52"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="52"/>
-      <c r="H35" s="52"/>
-      <c r="I35" s="52"/>
-      <c r="J35" s="52"/>
-      <c r="K35" s="52"/>
-      <c r="L35" s="52"/>
-    </row>
-    <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="85" t="s">
+      <c r="I34" s="90"/>
+      <c r="J34" s="90"/>
+      <c r="K34" s="90"/>
+    </row>
+    <row r="35" spans="2:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="93"/>
+      <c r="C35" s="93"/>
+      <c r="D35" s="25"/>
+    </row>
+    <row r="36" spans="2:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="115" t="s">
         <v>29</v>
       </c>
-      <c r="C36" s="86"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="87"/>
-      <c r="F36" s="87"/>
-      <c r="G36" s="87"/>
-      <c r="H36" s="87"/>
-      <c r="I36" s="87"/>
-      <c r="J36" s="87"/>
-      <c r="K36" s="88"/>
-    </row>
-    <row r="37" spans="1:12" ht="1.1499999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="1:12" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="90"/>
-      <c r="C38" s="91"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="24"/>
-      <c r="H38" s="25"/>
-      <c r="I38" s="89"/>
-      <c r="J38" s="89"/>
-      <c r="K38" s="89"/>
-    </row>
-    <row r="39" spans="1:12" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="90"/>
-      <c r="C39" s="91"/>
-      <c r="D39" s="27"/>
-      <c r="E39" s="22"/>
-      <c r="F39" s="23"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="25"/>
-      <c r="I39" s="89"/>
-      <c r="J39" s="89"/>
-      <c r="K39" s="89"/>
-    </row>
-    <row r="40" spans="1:12" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="92"/>
-      <c r="C40" s="92"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="22"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="25"/>
-      <c r="I40" s="89"/>
-      <c r="J40" s="89"/>
-      <c r="K40" s="89"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B41" s="93"/>
-      <c r="C41" s="93"/>
-      <c r="D41" s="27"/>
+      <c r="C36" s="44"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="43"/>
+    </row>
+    <row r="37" spans="2:11" ht="1.1499999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="94"/>
+      <c r="C37" s="94"/>
+      <c r="D37" s="25"/>
+    </row>
+    <row r="38" spans="2:11" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="91"/>
+      <c r="C38" s="92"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="23"/>
+      <c r="H38" s="24"/>
+      <c r="I38" s="90"/>
+      <c r="J38" s="90"/>
+      <c r="K38" s="90"/>
+    </row>
+    <row r="39" spans="2:11" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="91"/>
+      <c r="C39" s="92"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="23"/>
+      <c r="H39" s="24"/>
+      <c r="I39" s="90"/>
+      <c r="J39" s="90"/>
+      <c r="K39" s="90"/>
+    </row>
+    <row r="40" spans="2:11" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="95"/>
+      <c r="C40" s="95"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="90"/>
+      <c r="J40" s="90"/>
+      <c r="K40" s="90"/>
+    </row>
+    <row r="41" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="96"/>
+      <c r="C41" s="96"/>
+      <c r="D41" s="26"/>
       <c r="E41" s="12"/>
       <c r="F41" s="14"/>
       <c r="G41" s="14"/>
       <c r="H41" s="14"/>
-      <c r="I41" s="89"/>
-      <c r="J41" s="89"/>
-      <c r="K41" s="89"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B42" s="93"/>
-      <c r="C42" s="93"/>
-      <c r="D42" s="27"/>
+      <c r="I41" s="90"/>
+      <c r="J41" s="90"/>
+      <c r="K41" s="90"/>
+    </row>
+    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="96"/>
+      <c r="C42" s="96"/>
+      <c r="D42" s="26"/>
       <c r="E42" s="12"/>
       <c r="F42" s="13"/>
       <c r="G42" s="14"/>
       <c r="H42" s="15"/>
-      <c r="I42" s="89"/>
-      <c r="J42" s="89"/>
-      <c r="K42" s="89"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B43" s="93"/>
-      <c r="C43" s="93"/>
-      <c r="D43" s="27"/>
+      <c r="I42" s="90"/>
+      <c r="J42" s="90"/>
+      <c r="K42" s="90"/>
+    </row>
+    <row r="43" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="96"/>
+      <c r="C43" s="96"/>
+      <c r="D43" s="26"/>
       <c r="E43" s="12"/>
       <c r="F43" s="13"/>
       <c r="G43" s="14"/>
       <c r="H43" s="15"/>
-      <c r="I43" s="89"/>
-      <c r="J43" s="89"/>
-      <c r="K43" s="89"/>
-    </row>
-    <row r="44" spans="1:12" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="92"/>
-      <c r="C44" s="92"/>
-      <c r="D44" s="27"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="23"/>
-      <c r="G44" s="24"/>
-      <c r="H44" s="25"/>
-      <c r="I44" s="89"/>
-      <c r="J44" s="89"/>
-      <c r="K44" s="89"/>
-    </row>
-    <row r="45" spans="1:12" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="92"/>
-      <c r="C45" s="92"/>
-      <c r="D45" s="27"/>
-      <c r="E45" s="22"/>
-      <c r="F45" s="23"/>
-      <c r="G45" s="24"/>
-      <c r="H45" s="25"/>
-      <c r="I45" s="89"/>
-      <c r="J45" s="89"/>
-      <c r="K45" s="89"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B46" s="93"/>
-      <c r="C46" s="93"/>
-      <c r="D46" s="27"/>
+      <c r="I43" s="90"/>
+      <c r="J43" s="90"/>
+      <c r="K43" s="90"/>
+    </row>
+    <row r="44" spans="2:11" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="95"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="23"/>
+      <c r="H44" s="24"/>
+      <c r="I44" s="90"/>
+      <c r="J44" s="90"/>
+      <c r="K44" s="90"/>
+    </row>
+    <row r="45" spans="2:11" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="95"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="23"/>
+      <c r="H45" s="24"/>
+      <c r="I45" s="90"/>
+      <c r="J45" s="90"/>
+      <c r="K45" s="90"/>
+    </row>
+    <row r="46" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="96"/>
+      <c r="C46" s="96"/>
+      <c r="D46" s="26"/>
       <c r="E46" s="12"/>
       <c r="F46" s="13"/>
       <c r="G46" s="14"/>
       <c r="H46" s="15"/>
-      <c r="I46" s="89"/>
-      <c r="J46" s="89"/>
-      <c r="K46" s="89"/>
-    </row>
-    <row r="47" spans="1:12" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="94"/>
-      <c r="C47" s="94"/>
-      <c r="D47" s="27"/>
-      <c r="E47" s="22"/>
-      <c r="F47" s="23"/>
-      <c r="G47" s="22"/>
-      <c r="H47" s="37"/>
-      <c r="I47" s="89"/>
-      <c r="J47" s="89"/>
-      <c r="K47" s="89"/>
-    </row>
-    <row r="48" spans="1:12" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-    </row>
-    <row r="49" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="85" t="s">
+      <c r="I46" s="90"/>
+      <c r="J46" s="90"/>
+      <c r="K46" s="90"/>
+    </row>
+    <row r="47" spans="2:11" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="97"/>
+      <c r="C47" s="97"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="21"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="21"/>
+      <c r="H47" s="36"/>
+      <c r="I47" s="90"/>
+      <c r="J47" s="90"/>
+      <c r="K47" s="90"/>
+    </row>
+    <row r="48" spans="2:11" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="98"/>
+      <c r="C48" s="98"/>
+      <c r="D48" s="41"/>
+    </row>
+    <row r="49" spans="2:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="115" t="s">
         <v>30</v>
       </c>
-      <c r="C49" s="86"/>
-      <c r="D49" s="33"/>
-      <c r="E49" s="87"/>
-      <c r="F49" s="87"/>
-      <c r="G49" s="87"/>
-      <c r="H49" s="87"/>
-      <c r="I49" s="87"/>
-      <c r="J49" s="87"/>
-      <c r="K49" s="88"/>
-    </row>
-    <row r="50" spans="2:11" ht="2.25" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="C49" s="44"/>
+      <c r="D49" s="40"/>
+      <c r="E49" s="42"/>
+      <c r="F49" s="42"/>
+      <c r="G49" s="42"/>
+      <c r="H49" s="42"/>
+      <c r="I49" s="42"/>
+      <c r="J49" s="42"/>
+      <c r="K49" s="43"/>
+    </row>
+    <row r="50" spans="2:11" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="45"/>
+      <c r="C50" s="45"/>
+      <c r="D50" s="25"/>
+    </row>
     <row r="51" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B51" s="89"/>
-      <c r="C51" s="89"/>
-      <c r="D51" s="21"/>
+      <c r="B51" s="90"/>
+      <c r="C51" s="90"/>
+      <c r="D51" s="35"/>
       <c r="E51" s="9"/>
       <c r="F51" s="16"/>
-      <c r="G51" s="96"/>
-      <c r="H51" s="96"/>
-      <c r="I51" s="89"/>
-      <c r="J51" s="89"/>
-      <c r="K51" s="89"/>
+      <c r="G51" s="100"/>
+      <c r="H51" s="100"/>
+      <c r="I51" s="90"/>
+      <c r="J51" s="90"/>
+      <c r="K51" s="90"/>
     </row>
     <row r="52" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B52" s="101"/>
-      <c r="C52" s="102"/>
-      <c r="D52" s="21"/>
+      <c r="B52" s="105"/>
+      <c r="C52" s="106"/>
+      <c r="D52" s="35"/>
       <c r="E52" s="9"/>
       <c r="F52" s="6"/>
-      <c r="G52" s="96"/>
-      <c r="H52" s="96"/>
-      <c r="I52" s="89"/>
-      <c r="J52" s="89"/>
-      <c r="K52" s="89"/>
+      <c r="G52" s="100"/>
+      <c r="H52" s="100"/>
+      <c r="I52" s="90"/>
+      <c r="J52" s="90"/>
+      <c r="K52" s="90"/>
     </row>
     <row r="53" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B53" s="95"/>
-      <c r="C53" s="95"/>
-      <c r="D53" s="21"/>
+      <c r="B53" s="99"/>
+      <c r="C53" s="99"/>
+      <c r="D53" s="35"/>
       <c r="E53" s="9"/>
       <c r="F53" s="6"/>
-      <c r="G53" s="96"/>
-      <c r="H53" s="96"/>
-      <c r="I53" s="89"/>
-      <c r="J53" s="89"/>
-      <c r="K53" s="89"/>
+      <c r="G53" s="100"/>
+      <c r="H53" s="100"/>
+      <c r="I53" s="90"/>
+      <c r="J53" s="90"/>
+      <c r="K53" s="90"/>
     </row>
     <row r="54" spans="2:11" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E54" s="17"/>
       <c r="F54" s="17"/>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B55" s="97" t="s">
+      <c r="B55" s="101" t="s">
         <v>31</v>
       </c>
-      <c r="C55" s="98"/>
-      <c r="D55" s="98"/>
-      <c r="E55" s="98"/>
-      <c r="F55" s="98"/>
-      <c r="G55" s="98"/>
-      <c r="H55" s="98"/>
-      <c r="I55" s="98"/>
-      <c r="J55" s="98"/>
-      <c r="K55" s="99"/>
+      <c r="C55" s="102"/>
+      <c r="D55" s="102"/>
+      <c r="E55" s="102"/>
+      <c r="F55" s="102"/>
+      <c r="G55" s="102"/>
+      <c r="H55" s="102"/>
+      <c r="I55" s="102"/>
+      <c r="J55" s="102"/>
+      <c r="K55" s="103"/>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B56" s="105"/>
-      <c r="C56" s="106"/>
-      <c r="D56" s="106"/>
-      <c r="E56" s="106"/>
-      <c r="F56" s="106"/>
-      <c r="G56" s="106"/>
-      <c r="H56" s="106"/>
-      <c r="I56" s="106"/>
-      <c r="J56" s="106"/>
-      <c r="K56" s="107"/>
+      <c r="B56" s="109"/>
+      <c r="C56" s="110"/>
+      <c r="D56" s="110"/>
+      <c r="E56" s="110"/>
+      <c r="F56" s="110"/>
+      <c r="G56" s="110"/>
+      <c r="H56" s="110"/>
+      <c r="I56" s="110"/>
+      <c r="J56" s="110"/>
+      <c r="K56" s="111"/>
     </row>
     <row r="57" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="105"/>
-      <c r="C57" s="106"/>
-      <c r="D57" s="106"/>
-      <c r="E57" s="106"/>
-      <c r="F57" s="106"/>
-      <c r="G57" s="106"/>
-      <c r="H57" s="106"/>
-      <c r="I57" s="106"/>
-      <c r="J57" s="106"/>
-      <c r="K57" s="107"/>
+      <c r="B57" s="109"/>
+      <c r="C57" s="110"/>
+      <c r="D57" s="110"/>
+      <c r="E57" s="110"/>
+      <c r="F57" s="110"/>
+      <c r="G57" s="110"/>
+      <c r="H57" s="110"/>
+      <c r="I57" s="110"/>
+      <c r="J57" s="110"/>
+      <c r="K57" s="111"/>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B58" s="105"/>
-      <c r="C58" s="106"/>
-      <c r="D58" s="106"/>
-      <c r="E58" s="106"/>
-      <c r="F58" s="106"/>
-      <c r="G58" s="106"/>
-      <c r="H58" s="106"/>
-      <c r="I58" s="106"/>
-      <c r="J58" s="106"/>
-      <c r="K58" s="107"/>
+      <c r="B58" s="109"/>
+      <c r="C58" s="110"/>
+      <c r="D58" s="110"/>
+      <c r="E58" s="110"/>
+      <c r="F58" s="110"/>
+      <c r="G58" s="110"/>
+      <c r="H58" s="110"/>
+      <c r="I58" s="110"/>
+      <c r="J58" s="110"/>
+      <c r="K58" s="111"/>
     </row>
     <row r="59" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="108"/>
-      <c r="C59" s="109"/>
-      <c r="D59" s="109"/>
-      <c r="E59" s="109"/>
-      <c r="F59" s="109"/>
-      <c r="G59" s="109"/>
-      <c r="H59" s="109"/>
-      <c r="I59" s="109"/>
-      <c r="J59" s="109"/>
-      <c r="K59" s="110"/>
+      <c r="B59" s="112"/>
+      <c r="C59" s="113"/>
+      <c r="D59" s="113"/>
+      <c r="E59" s="113"/>
+      <c r="F59" s="113"/>
+      <c r="G59" s="113"/>
+      <c r="H59" s="113"/>
+      <c r="I59" s="113"/>
+      <c r="J59" s="113"/>
+      <c r="K59" s="114"/>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B60" s="34"/>
-      <c r="C60" s="34"/>
-      <c r="D60" s="34"/>
-      <c r="E60" s="34"/>
-      <c r="F60" s="34"/>
-      <c r="G60" s="34"/>
-      <c r="H60" s="34"/>
-      <c r="I60" s="34"/>
-      <c r="J60" s="34"/>
-      <c r="K60" s="34"/>
+      <c r="B60" s="33"/>
+      <c r="C60" s="33"/>
+      <c r="D60" s="33"/>
+      <c r="E60" s="33"/>
+      <c r="F60" s="33"/>
+      <c r="G60" s="33"/>
+      <c r="H60" s="33"/>
+      <c r="I60" s="33"/>
+      <c r="J60" s="33"/>
+      <c r="K60" s="33"/>
     </row>
     <row r="61" spans="2:11" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="100" t="s">
+      <c r="B61" s="104" t="s">
         <v>32</v>
       </c>
-      <c r="C61" s="100"/>
-      <c r="D61" s="100"/>
-      <c r="E61" s="100"/>
-      <c r="F61" s="100"/>
-      <c r="G61" s="100"/>
-      <c r="H61" s="100"/>
-      <c r="I61" s="100"/>
-      <c r="J61" s="100"/>
-      <c r="K61" s="100"/>
+      <c r="C61" s="104"/>
+      <c r="D61" s="104"/>
+      <c r="E61" s="104"/>
+      <c r="F61" s="104"/>
+      <c r="G61" s="104"/>
+      <c r="H61" s="104"/>
+      <c r="I61" s="104"/>
+      <c r="J61" s="104"/>
+      <c r="K61" s="104"/>
     </row>
     <row r="62" spans="2:11" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="100" t="s">
+      <c r="B62" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="C62" s="100"/>
-      <c r="D62" s="100"/>
-      <c r="E62" s="100"/>
-      <c r="F62" s="100"/>
-      <c r="G62" s="100"/>
-      <c r="H62" s="100"/>
-      <c r="I62" s="100"/>
-      <c r="J62" s="100"/>
-      <c r="K62" s="100"/>
+      <c r="C62" s="104"/>
+      <c r="D62" s="104"/>
+      <c r="E62" s="104"/>
+      <c r="F62" s="104"/>
+      <c r="G62" s="104"/>
+      <c r="H62" s="104"/>
+      <c r="I62" s="104"/>
+      <c r="J62" s="104"/>
+      <c r="K62" s="104"/>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B63" s="35" t="s">
+      <c r="B63" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="C63" s="35"/>
-      <c r="D63" s="35"/>
-      <c r="E63" s="35"/>
-      <c r="F63" s="35"/>
-      <c r="G63" s="35"/>
-      <c r="H63" s="35"/>
-      <c r="I63" s="35"/>
-      <c r="J63" s="35"/>
-      <c r="K63" s="35"/>
+      <c r="C63" s="34"/>
+      <c r="D63" s="34"/>
+      <c r="E63" s="34"/>
+      <c r="F63" s="34"/>
+      <c r="G63" s="34"/>
+      <c r="H63" s="34"/>
+      <c r="I63" s="34"/>
+      <c r="J63" s="34"/>
+      <c r="K63" s="34"/>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B64" s="35" t="s">
+      <c r="B64" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="C64" s="35"/>
-      <c r="D64" s="35"/>
-      <c r="E64" s="35"/>
-      <c r="F64" s="35"/>
-      <c r="G64" s="35"/>
-      <c r="H64" s="35"/>
-      <c r="I64" s="35"/>
-      <c r="J64" s="35"/>
-      <c r="K64" s="35"/>
+      <c r="C64" s="34"/>
+      <c r="D64" s="34"/>
+      <c r="E64" s="34"/>
+      <c r="F64" s="34"/>
+      <c r="G64" s="34"/>
+      <c r="H64" s="34"/>
+      <c r="I64" s="34"/>
+      <c r="J64" s="34"/>
+      <c r="K64" s="34"/>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B65" s="104" t="s">
+      <c r="B65" s="108" t="s">
         <v>36</v>
       </c>
-      <c r="C65" s="104"/>
-      <c r="D65" s="104"/>
-      <c r="E65" s="104"/>
-      <c r="F65" s="104"/>
-      <c r="G65" s="104"/>
-      <c r="H65" s="104"/>
-      <c r="I65" s="104"/>
-      <c r="J65" s="104"/>
-      <c r="K65" s="104"/>
+      <c r="C65" s="108"/>
+      <c r="D65" s="108"/>
+      <c r="E65" s="108"/>
+      <c r="F65" s="108"/>
+      <c r="G65" s="108"/>
+      <c r="H65" s="108"/>
+      <c r="I65" s="108"/>
+      <c r="J65" s="108"/>
+      <c r="K65" s="108"/>
     </row>
     <row r="66" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="104"/>
-      <c r="C66" s="104"/>
-      <c r="D66" s="104"/>
-      <c r="E66" s="104"/>
-      <c r="F66" s="104"/>
-      <c r="G66" s="104"/>
-      <c r="H66" s="104"/>
-      <c r="I66" s="104"/>
-      <c r="J66" s="104"/>
-      <c r="K66" s="104"/>
+      <c r="B66" s="108"/>
+      <c r="C66" s="108"/>
+      <c r="D66" s="108"/>
+      <c r="E66" s="108"/>
+      <c r="F66" s="108"/>
+      <c r="G66" s="108"/>
+      <c r="H66" s="108"/>
+      <c r="I66" s="108"/>
+      <c r="J66" s="108"/>
+      <c r="K66" s="108"/>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H70" s="52"/>
-      <c r="I70" s="52"/>
-      <c r="J70" s="52"/>
+      <c r="H70" s="57"/>
+      <c r="I70" s="57"/>
+      <c r="J70" s="57"/>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D72" s="35"/>
-      <c r="E72" s="35"/>
-      <c r="F72" s="35"/>
-      <c r="H72" s="52"/>
-      <c r="I72" s="52"/>
-      <c r="J72" s="52"/>
+      <c r="D72" s="34"/>
+      <c r="E72" s="34"/>
+      <c r="F72" s="34"/>
+      <c r="H72" s="57"/>
+      <c r="I72" s="57"/>
+      <c r="J72" s="57"/>
     </row>
     <row r="73" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="52"/>
-      <c r="C73" s="52"/>
-      <c r="D73" s="52"/>
-      <c r="E73" s="52"/>
-      <c r="G73" s="111"/>
-      <c r="H73" s="111"/>
-      <c r="I73" s="111"/>
-      <c r="J73" s="111"/>
+      <c r="B73" s="57"/>
+      <c r="C73" s="57"/>
+      <c r="D73" s="57"/>
+      <c r="E73" s="57"/>
+      <c r="G73" s="57"/>
+      <c r="H73" s="57"/>
+      <c r="I73" s="57"/>
+      <c r="J73" s="57"/>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B74" s="52" t="s">
+      <c r="B74" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="C74" s="52"/>
-      <c r="D74" s="52"/>
-      <c r="E74" s="52"/>
-      <c r="G74" s="52" t="s">
+      <c r="C74" s="57"/>
+      <c r="D74" s="57"/>
+      <c r="E74" s="57"/>
+      <c r="G74" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="H74" s="52"/>
-      <c r="I74" s="52"/>
-      <c r="J74" s="52"/>
+      <c r="H74" s="57"/>
+      <c r="I74" s="57"/>
+      <c r="J74" s="57"/>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B75" s="52"/>
-      <c r="C75" s="52"/>
-      <c r="D75" s="52"/>
-      <c r="E75" s="52"/>
-      <c r="G75" s="52"/>
-      <c r="H75" s="52"/>
-      <c r="I75" s="52"/>
-      <c r="J75" s="52"/>
+      <c r="B75" s="57"/>
+      <c r="C75" s="57"/>
+      <c r="D75" s="57"/>
+      <c r="E75" s="57"/>
+      <c r="G75" s="57"/>
+      <c r="H75" s="57"/>
+      <c r="I75" s="57"/>
+      <c r="J75" s="57"/>
     </row>
     <row r="78" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A78" s="44" t="s">
+      <c r="A78" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B78" s="44"/>
-      <c r="C78" s="44"/>
-      <c r="D78" s="44" t="s">
+      <c r="B78" s="49"/>
+      <c r="C78" s="49"/>
+      <c r="D78" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="E78" s="44"/>
-      <c r="F78" s="44"/>
-      <c r="G78" s="44"/>
-      <c r="J78" s="39" t="s">
+      <c r="E78" s="49"/>
+      <c r="F78" s="49"/>
+      <c r="G78" s="49"/>
+      <c r="J78" s="38" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="D79" s="103" t="s">
+      <c r="D79" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="E79" s="103"/>
-      <c r="F79" s="103"/>
-      <c r="G79" s="103"/>
-      <c r="J79" s="40" t="s">
+      <c r="E79" s="107"/>
+      <c r="F79" s="107"/>
+      <c r="G79" s="107"/>
+      <c r="J79" s="39" t="s">
         <v>40</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="93">
+  <mergeCells count="90">
     <mergeCell ref="D78:G78"/>
     <mergeCell ref="D79:G79"/>
     <mergeCell ref="A78:C78"/>
@@ -2476,8 +2531,7 @@
     <mergeCell ref="I46:K46"/>
     <mergeCell ref="B47:C47"/>
     <mergeCell ref="I47:K47"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="E49:K49"/>
+    <mergeCell ref="B48:C48"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="I43:K43"/>
     <mergeCell ref="B44:C44"/>
@@ -2490,6 +2544,10 @@
     <mergeCell ref="I41:K41"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="I42:K42"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="I31:K31"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="I39:K39"/>
     <mergeCell ref="B32:C32"/>
@@ -2498,17 +2556,10 @@
     <mergeCell ref="I33:K33"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="I34:K34"/>
-    <mergeCell ref="A35:L35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="E36:K36"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="I38:K38"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="E28:K28"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="E22:G22"/>
     <mergeCell ref="I22:K22"/>
@@ -2525,6 +2576,7 @@
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="F20:I20"/>
     <mergeCell ref="J20:K20"/>
+    <mergeCell ref="B50:C50"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="B7:K7"/>
     <mergeCell ref="B8:K8"/>

--- a/modules/laboratorio/muestra/plantilla/CSJ-DRDYCS-LAYS – R - 2- RESULTADOS ANALISIS DE AGUAS.xlsx
+++ b/modules/laboratorio/muestra/plantilla/CSJ-DRDYCS-LAYS – R - 2- RESULTADOS ANALISIS DE AGUAS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SISTEMAS\gestionTI2026\modules\laboratorio\muestra\plantilla\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA258392-F298-4D20-8882-E39FC123C2FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB56DCC5-30D8-49DF-BFD2-96ABBF09AFF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="9915" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FORMATO 002 -2024" sheetId="1" r:id="rId1"/>
@@ -1059,6 +1059,183 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1071,15 +1248,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1093,184 +1261,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1701,8 +1701,8 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
       <c r="D2" s="27" t="s">
         <v>0</v>
       </c>
@@ -1710,14 +1710,14 @@
       <c r="G2" s="29"/>
       <c r="H2" s="29"/>
       <c r="I2" s="29"/>
-      <c r="J2" s="58" t="s">
+      <c r="J2" s="113" t="s">
         <v>37</v>
       </c>
-      <c r="K2" s="46"/>
+      <c r="K2" s="105"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
       <c r="D3" s="27" t="s">
         <v>1</v>
       </c>
@@ -1725,12 +1725,12 @@
       <c r="G3" s="29"/>
       <c r="H3" s="29"/>
       <c r="I3" s="29"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="47"/>
+      <c r="J3" s="113"/>
+      <c r="K3" s="106"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="55"/>
       <c r="D4" s="27" t="s">
         <v>2</v>
       </c>
@@ -1742,8 +1742,8 @@
       <c r="K4" s="29"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
       <c r="D5" s="27" t="s">
         <v>3</v>
       </c>
@@ -1756,32 +1756,32 @@
     </row>
     <row r="6" spans="2:13" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="2:13" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="107"/>
+      <c r="E7" s="107"/>
+      <c r="F7" s="107"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
     </row>
     <row r="8" spans="2:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="49" t="s">
+      <c r="B8" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="49"/>
-      <c r="K8" s="49"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
+      <c r="J8" s="46"/>
+      <c r="K8" s="46"/>
     </row>
     <row r="9" spans="2:13" ht="7.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E9" s="30"/>
@@ -1793,10 +1793,10 @@
       <c r="K9" s="30"/>
     </row>
     <row r="10" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="50" t="s">
+      <c r="B10" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="51"/>
+      <c r="C10" s="74"/>
       <c r="D10" s="1" t="s">
         <v>7</v>
       </c>
@@ -1818,38 +1818,38 @@
       <c r="D11" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
+      <c r="E11" s="115"/>
+      <c r="F11" s="115"/>
     </row>
     <row r="12" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="50" t="s">
+      <c r="B12" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="59"/>
-      <c r="D12" s="60"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61"/>
-      <c r="J12" s="61"/>
-      <c r="K12" s="62"/>
+      <c r="C12" s="100"/>
+      <c r="D12" s="75"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="76"/>
+      <c r="J12" s="76"/>
+      <c r="K12" s="77"/>
     </row>
     <row r="13" spans="2:13" ht="4.1500000000000004" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="50" t="s">
+      <c r="B14" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="59"/>
-      <c r="D14" s="63" t="s">
+      <c r="C14" s="100"/>
+      <c r="D14" s="114" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="63"/>
+      <c r="E14" s="114"/>
       <c r="F14" s="18"/>
-      <c r="G14" s="63" t="s">
+      <c r="G14" s="114" t="s">
         <v>13</v>
       </c>
-      <c r="H14" s="63"/>
+      <c r="H14" s="114"/>
       <c r="I14" s="3"/>
       <c r="J14" s="1" t="s">
         <v>14</v>
@@ -1860,19 +1860,19 @@
       <c r="F15" s="17"/>
     </row>
     <row r="16" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="52" t="s">
+      <c r="B16" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="53"/>
-      <c r="D16" s="54" t="s">
+      <c r="C16" s="109"/>
+      <c r="D16" s="110" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="55"/>
+      <c r="E16" s="111"/>
       <c r="F16" s="18"/>
-      <c r="G16" s="56" t="s">
+      <c r="G16" s="112" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="55"/>
+      <c r="H16" s="111"/>
       <c r="I16" s="18"/>
       <c r="J16" s="1" t="s">
         <v>18</v>
@@ -1884,92 +1884,92 @@
       <c r="M17" s="31"/>
     </row>
     <row r="18" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="50" t="s">
+      <c r="B18" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="59"/>
-      <c r="D18" s="65" t="s">
+      <c r="C18" s="100"/>
+      <c r="D18" s="101" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="61"/>
-      <c r="F18" s="61"/>
-      <c r="G18" s="61"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="61"/>
-      <c r="J18" s="61"/>
-      <c r="K18" s="62"/>
+      <c r="E18" s="76"/>
+      <c r="F18" s="76"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="76"/>
+      <c r="I18" s="76"/>
+      <c r="J18" s="76"/>
+      <c r="K18" s="77"/>
     </row>
     <row r="19" spans="2:13" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="50" t="s">
+      <c r="B20" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="59"/>
-      <c r="D20" s="66"/>
-      <c r="E20" s="61"/>
-      <c r="F20" s="67" t="s">
+      <c r="C20" s="100"/>
+      <c r="D20" s="102"/>
+      <c r="E20" s="76"/>
+      <c r="F20" s="93" t="s">
         <v>20</v>
       </c>
-      <c r="G20" s="67"/>
-      <c r="H20" s="67"/>
-      <c r="I20" s="67"/>
-      <c r="J20" s="68"/>
-      <c r="K20" s="61"/>
+      <c r="G20" s="93"/>
+      <c r="H20" s="93"/>
+      <c r="I20" s="93"/>
+      <c r="J20" s="103"/>
+      <c r="K20" s="76"/>
     </row>
     <row r="21" spans="2:13" ht="4.1500000000000004" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="22" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="50" t="s">
+      <c r="B22" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="51"/>
+      <c r="C22" s="74"/>
       <c r="D22" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="60"/>
-      <c r="F22" s="61"/>
-      <c r="G22" s="62"/>
+      <c r="E22" s="75"/>
+      <c r="F22" s="76"/>
+      <c r="G22" s="77"/>
       <c r="H22" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="I22" s="61"/>
-      <c r="J22" s="61"/>
-      <c r="K22" s="61"/>
+      <c r="I22" s="76"/>
+      <c r="J22" s="76"/>
+      <c r="K22" s="76"/>
     </row>
     <row r="23" spans="2:13" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="2:13" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="69" t="s">
+      <c r="B24" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="70"/>
-      <c r="D24" s="75" t="s">
+      <c r="C24" s="79"/>
+      <c r="D24" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="E24" s="78"/>
-      <c r="F24" s="79"/>
-      <c r="G24" s="78"/>
-      <c r="H24" s="79"/>
-      <c r="I24" s="80" t="s">
+      <c r="E24" s="87"/>
+      <c r="F24" s="88"/>
+      <c r="G24" s="87"/>
+      <c r="H24" s="88"/>
+      <c r="I24" s="89" t="s">
         <v>26</v>
       </c>
-      <c r="J24" s="81"/>
-      <c r="K24" s="82"/>
+      <c r="J24" s="90"/>
+      <c r="K24" s="91"/>
     </row>
     <row r="25" spans="2:13" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="71"/>
-      <c r="C25" s="72"/>
-      <c r="D25" s="76"/>
-      <c r="E25" s="88"/>
-      <c r="F25" s="89"/>
-      <c r="G25" s="88"/>
-      <c r="H25" s="89"/>
-      <c r="I25" s="83"/>
-      <c r="J25" s="67"/>
-      <c r="K25" s="84"/>
+      <c r="B25" s="80"/>
+      <c r="C25" s="81"/>
+      <c r="D25" s="85"/>
+      <c r="E25" s="98"/>
+      <c r="F25" s="99"/>
+      <c r="G25" s="98"/>
+      <c r="H25" s="99"/>
+      <c r="I25" s="92"/>
+      <c r="J25" s="93"/>
+      <c r="K25" s="94"/>
     </row>
     <row r="26" spans="2:13" ht="22.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="73"/>
-      <c r="C26" s="74"/>
-      <c r="D26" s="77"/>
+      <c r="B26" s="82"/>
+      <c r="C26" s="83"/>
+      <c r="D26" s="86"/>
       <c r="E26" s="4" t="s">
         <v>43</v>
       </c>
@@ -1982,13 +1982,13 @@
       <c r="H26" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I26" s="85"/>
-      <c r="J26" s="86"/>
-      <c r="K26" s="87"/>
+      <c r="I26" s="95"/>
+      <c r="J26" s="96"/>
+      <c r="K26" s="97"/>
     </row>
     <row r="27" spans="2:13" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="28" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="115" t="s">
+      <c r="B28" s="45" t="s">
         <v>27</v>
       </c>
       <c r="C28" s="44"/>
@@ -2003,72 +2003,72 @@
     </row>
     <row r="29" spans="2:13" ht="0.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B30" s="90"/>
-      <c r="C30" s="90"/>
+      <c r="B30" s="57"/>
+      <c r="C30" s="57"/>
       <c r="D30" s="35"/>
       <c r="E30" s="7"/>
       <c r="F30" s="8"/>
       <c r="G30" s="7"/>
       <c r="H30" s="8"/>
-      <c r="I30" s="90"/>
-      <c r="J30" s="90"/>
-      <c r="K30" s="90"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
     </row>
     <row r="31" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="90"/>
-      <c r="C31" s="90"/>
+      <c r="B31" s="57"/>
+      <c r="C31" s="57"/>
       <c r="D31" s="35"/>
       <c r="E31" s="9"/>
       <c r="F31" s="10"/>
       <c r="G31" s="11"/>
       <c r="H31" s="10"/>
-      <c r="I31" s="90"/>
-      <c r="J31" s="90"/>
-      <c r="K31" s="90"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="57"/>
+      <c r="K31" s="57"/>
     </row>
     <row r="32" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="90"/>
-      <c r="C32" s="90"/>
+      <c r="B32" s="57"/>
+      <c r="C32" s="57"/>
       <c r="D32" s="35"/>
       <c r="E32" s="9"/>
       <c r="F32" s="10"/>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
-      <c r="I32" s="90"/>
-      <c r="J32" s="90"/>
-      <c r="K32" s="90"/>
+      <c r="I32" s="57"/>
+      <c r="J32" s="57"/>
+      <c r="K32" s="57"/>
     </row>
     <row r="33" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="90"/>
-      <c r="C33" s="90"/>
+      <c r="B33" s="57"/>
+      <c r="C33" s="57"/>
       <c r="D33" s="35"/>
       <c r="E33" s="9"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="8"/>
-      <c r="I33" s="90"/>
-      <c r="J33" s="90"/>
-      <c r="K33" s="90"/>
+      <c r="I33" s="57"/>
+      <c r="J33" s="57"/>
+      <c r="K33" s="57"/>
     </row>
     <row r="34" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="90"/>
-      <c r="C34" s="90"/>
+      <c r="B34" s="57"/>
+      <c r="C34" s="57"/>
       <c r="D34" s="37"/>
       <c r="E34" s="9"/>
       <c r="F34" s="8"/>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
-      <c r="I34" s="90"/>
-      <c r="J34" s="90"/>
-      <c r="K34" s="90"/>
+      <c r="I34" s="57"/>
+      <c r="J34" s="57"/>
+      <c r="K34" s="57"/>
     </row>
     <row r="35" spans="2:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
-      <c r="C35" s="93"/>
+      <c r="B35" s="71"/>
+      <c r="C35" s="71"/>
       <c r="D35" s="25"/>
     </row>
     <row r="36" spans="2:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="115" t="s">
+      <c r="B36" s="45" t="s">
         <v>29</v>
       </c>
       <c r="C36" s="44"/>
@@ -2082,137 +2082,137 @@
       <c r="K36" s="43"/>
     </row>
     <row r="37" spans="2:11" ht="1.1499999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="94"/>
-      <c r="C37" s="94"/>
+      <c r="B37" s="72"/>
+      <c r="C37" s="72"/>
       <c r="D37" s="25"/>
     </row>
     <row r="38" spans="2:11" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="91"/>
-      <c r="C38" s="92"/>
+      <c r="B38" s="69"/>
+      <c r="C38" s="70"/>
       <c r="D38" s="26"/>
       <c r="E38" s="21"/>
       <c r="F38" s="22"/>
       <c r="G38" s="23"/>
       <c r="H38" s="24"/>
-      <c r="I38" s="90"/>
-      <c r="J38" s="90"/>
-      <c r="K38" s="90"/>
+      <c r="I38" s="57"/>
+      <c r="J38" s="57"/>
+      <c r="K38" s="57"/>
     </row>
     <row r="39" spans="2:11" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="91"/>
-      <c r="C39" s="92"/>
+      <c r="B39" s="69"/>
+      <c r="C39" s="70"/>
       <c r="D39" s="26"/>
       <c r="E39" s="21"/>
       <c r="F39" s="22"/>
       <c r="G39" s="23"/>
       <c r="H39" s="24"/>
-      <c r="I39" s="90"/>
-      <c r="J39" s="90"/>
-      <c r="K39" s="90"/>
+      <c r="I39" s="57"/>
+      <c r="J39" s="57"/>
+      <c r="K39" s="57"/>
     </row>
     <row r="40" spans="2:11" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="95"/>
-      <c r="C40" s="95"/>
+      <c r="B40" s="68"/>
+      <c r="C40" s="68"/>
       <c r="D40" s="26"/>
       <c r="E40" s="21"/>
       <c r="F40" s="22"/>
       <c r="G40" s="23"/>
       <c r="H40" s="24"/>
-      <c r="I40" s="90"/>
-      <c r="J40" s="90"/>
-      <c r="K40" s="90"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="57"/>
+      <c r="K40" s="57"/>
     </row>
     <row r="41" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="96"/>
-      <c r="C41" s="96"/>
+      <c r="B41" s="65"/>
+      <c r="C41" s="65"/>
       <c r="D41" s="26"/>
       <c r="E41" s="12"/>
       <c r="F41" s="14"/>
       <c r="G41" s="14"/>
       <c r="H41" s="14"/>
-      <c r="I41" s="90"/>
-      <c r="J41" s="90"/>
-      <c r="K41" s="90"/>
+      <c r="I41" s="57"/>
+      <c r="J41" s="57"/>
+      <c r="K41" s="57"/>
     </row>
     <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="96"/>
-      <c r="C42" s="96"/>
+      <c r="B42" s="65"/>
+      <c r="C42" s="65"/>
       <c r="D42" s="26"/>
       <c r="E42" s="12"/>
       <c r="F42" s="13"/>
       <c r="G42" s="14"/>
       <c r="H42" s="15"/>
-      <c r="I42" s="90"/>
-      <c r="J42" s="90"/>
-      <c r="K42" s="90"/>
+      <c r="I42" s="57"/>
+      <c r="J42" s="57"/>
+      <c r="K42" s="57"/>
     </row>
     <row r="43" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="96"/>
-      <c r="C43" s="96"/>
+      <c r="B43" s="65"/>
+      <c r="C43" s="65"/>
       <c r="D43" s="26"/>
       <c r="E43" s="12"/>
       <c r="F43" s="13"/>
       <c r="G43" s="14"/>
       <c r="H43" s="15"/>
-      <c r="I43" s="90"/>
-      <c r="J43" s="90"/>
-      <c r="K43" s="90"/>
+      <c r="I43" s="57"/>
+      <c r="J43" s="57"/>
+      <c r="K43" s="57"/>
     </row>
     <row r="44" spans="2:11" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="95"/>
-      <c r="C44" s="95"/>
+      <c r="B44" s="68"/>
+      <c r="C44" s="68"/>
       <c r="D44" s="26"/>
       <c r="E44" s="21"/>
       <c r="F44" s="22"/>
       <c r="G44" s="23"/>
       <c r="H44" s="24"/>
-      <c r="I44" s="90"/>
-      <c r="J44" s="90"/>
-      <c r="K44" s="90"/>
+      <c r="I44" s="57"/>
+      <c r="J44" s="57"/>
+      <c r="K44" s="57"/>
     </row>
     <row r="45" spans="2:11" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="95"/>
-      <c r="C45" s="95"/>
+      <c r="B45" s="68"/>
+      <c r="C45" s="68"/>
       <c r="D45" s="26"/>
       <c r="E45" s="21"/>
       <c r="F45" s="22"/>
       <c r="G45" s="23"/>
       <c r="H45" s="24"/>
-      <c r="I45" s="90"/>
-      <c r="J45" s="90"/>
-      <c r="K45" s="90"/>
+      <c r="I45" s="57"/>
+      <c r="J45" s="57"/>
+      <c r="K45" s="57"/>
     </row>
     <row r="46" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="96"/>
-      <c r="C46" s="96"/>
+      <c r="B46" s="65"/>
+      <c r="C46" s="65"/>
       <c r="D46" s="26"/>
       <c r="E46" s="12"/>
       <c r="F46" s="13"/>
       <c r="G46" s="14"/>
       <c r="H46" s="15"/>
-      <c r="I46" s="90"/>
-      <c r="J46" s="90"/>
-      <c r="K46" s="90"/>
+      <c r="I46" s="57"/>
+      <c r="J46" s="57"/>
+      <c r="K46" s="57"/>
     </row>
     <row r="47" spans="2:11" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="97"/>
-      <c r="C47" s="97"/>
+      <c r="B47" s="66"/>
+      <c r="C47" s="66"/>
       <c r="D47" s="26"/>
       <c r="E47" s="21"/>
       <c r="F47" s="22"/>
       <c r="G47" s="21"/>
       <c r="H47" s="36"/>
-      <c r="I47" s="90"/>
-      <c r="J47" s="90"/>
-      <c r="K47" s="90"/>
+      <c r="I47" s="57"/>
+      <c r="J47" s="57"/>
+      <c r="K47" s="57"/>
     </row>
     <row r="48" spans="2:11" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="98"/>
-      <c r="C48" s="98"/>
+      <c r="B48" s="67"/>
+      <c r="C48" s="67"/>
       <c r="D48" s="41"/>
     </row>
     <row r="49" spans="2:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="115" t="s">
+      <c r="B49" s="45" t="s">
         <v>30</v>
       </c>
       <c r="C49" s="44"/>
@@ -2226,111 +2226,111 @@
       <c r="K49" s="43"/>
     </row>
     <row r="50" spans="2:11" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="45"/>
-      <c r="C50" s="45"/>
+      <c r="B50" s="104"/>
+      <c r="C50" s="104"/>
       <c r="D50" s="25"/>
     </row>
     <row r="51" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B51" s="90"/>
-      <c r="C51" s="90"/>
+      <c r="B51" s="57"/>
+      <c r="C51" s="57"/>
       <c r="D51" s="35"/>
       <c r="E51" s="9"/>
       <c r="F51" s="16"/>
-      <c r="G51" s="100"/>
-      <c r="H51" s="100"/>
-      <c r="I51" s="90"/>
-      <c r="J51" s="90"/>
-      <c r="K51" s="90"/>
+      <c r="G51" s="58"/>
+      <c r="H51" s="58"/>
+      <c r="I51" s="57"/>
+      <c r="J51" s="57"/>
+      <c r="K51" s="57"/>
     </row>
     <row r="52" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B52" s="105"/>
-      <c r="C52" s="106"/>
+      <c r="B52" s="59"/>
+      <c r="C52" s="60"/>
       <c r="D52" s="35"/>
       <c r="E52" s="9"/>
       <c r="F52" s="6"/>
-      <c r="G52" s="100"/>
-      <c r="H52" s="100"/>
-      <c r="I52" s="90"/>
-      <c r="J52" s="90"/>
-      <c r="K52" s="90"/>
+      <c r="G52" s="58"/>
+      <c r="H52" s="58"/>
+      <c r="I52" s="57"/>
+      <c r="J52" s="57"/>
+      <c r="K52" s="57"/>
     </row>
     <row r="53" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B53" s="99"/>
-      <c r="C53" s="99"/>
+      <c r="B53" s="61"/>
+      <c r="C53" s="61"/>
       <c r="D53" s="35"/>
       <c r="E53" s="9"/>
       <c r="F53" s="6"/>
-      <c r="G53" s="100"/>
-      <c r="H53" s="100"/>
-      <c r="I53" s="90"/>
-      <c r="J53" s="90"/>
-      <c r="K53" s="90"/>
+      <c r="G53" s="58"/>
+      <c r="H53" s="58"/>
+      <c r="I53" s="57"/>
+      <c r="J53" s="57"/>
+      <c r="K53" s="57"/>
     </row>
     <row r="54" spans="2:11" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E54" s="17"/>
       <c r="F54" s="17"/>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B55" s="101" t="s">
+      <c r="B55" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="C55" s="102"/>
-      <c r="D55" s="102"/>
-      <c r="E55" s="102"/>
-      <c r="F55" s="102"/>
-      <c r="G55" s="102"/>
-      <c r="H55" s="102"/>
-      <c r="I55" s="102"/>
-      <c r="J55" s="102"/>
-      <c r="K55" s="103"/>
+      <c r="C55" s="63"/>
+      <c r="D55" s="63"/>
+      <c r="E55" s="63"/>
+      <c r="F55" s="63"/>
+      <c r="G55" s="63"/>
+      <c r="H55" s="63"/>
+      <c r="I55" s="63"/>
+      <c r="J55" s="63"/>
+      <c r="K55" s="64"/>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B56" s="109"/>
-      <c r="C56" s="110"/>
-      <c r="D56" s="110"/>
-      <c r="E56" s="110"/>
-      <c r="F56" s="110"/>
-      <c r="G56" s="110"/>
-      <c r="H56" s="110"/>
-      <c r="I56" s="110"/>
-      <c r="J56" s="110"/>
-      <c r="K56" s="111"/>
+      <c r="B56" s="49"/>
+      <c r="C56" s="50"/>
+      <c r="D56" s="50"/>
+      <c r="E56" s="50"/>
+      <c r="F56" s="50"/>
+      <c r="G56" s="50"/>
+      <c r="H56" s="50"/>
+      <c r="I56" s="50"/>
+      <c r="J56" s="50"/>
+      <c r="K56" s="51"/>
     </row>
     <row r="57" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="109"/>
-      <c r="C57" s="110"/>
-      <c r="D57" s="110"/>
-      <c r="E57" s="110"/>
-      <c r="F57" s="110"/>
-      <c r="G57" s="110"/>
-      <c r="H57" s="110"/>
-      <c r="I57" s="110"/>
-      <c r="J57" s="110"/>
-      <c r="K57" s="111"/>
+      <c r="B57" s="49"/>
+      <c r="C57" s="50"/>
+      <c r="D57" s="50"/>
+      <c r="E57" s="50"/>
+      <c r="F57" s="50"/>
+      <c r="G57" s="50"/>
+      <c r="H57" s="50"/>
+      <c r="I57" s="50"/>
+      <c r="J57" s="50"/>
+      <c r="K57" s="51"/>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B58" s="109"/>
-      <c r="C58" s="110"/>
-      <c r="D58" s="110"/>
-      <c r="E58" s="110"/>
-      <c r="F58" s="110"/>
-      <c r="G58" s="110"/>
-      <c r="H58" s="110"/>
-      <c r="I58" s="110"/>
-      <c r="J58" s="110"/>
-      <c r="K58" s="111"/>
+      <c r="B58" s="49"/>
+      <c r="C58" s="50"/>
+      <c r="D58" s="50"/>
+      <c r="E58" s="50"/>
+      <c r="F58" s="50"/>
+      <c r="G58" s="50"/>
+      <c r="H58" s="50"/>
+      <c r="I58" s="50"/>
+      <c r="J58" s="50"/>
+      <c r="K58" s="51"/>
     </row>
     <row r="59" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="112"/>
-      <c r="C59" s="113"/>
-      <c r="D59" s="113"/>
-      <c r="E59" s="113"/>
-      <c r="F59" s="113"/>
-      <c r="G59" s="113"/>
-      <c r="H59" s="113"/>
-      <c r="I59" s="113"/>
-      <c r="J59" s="113"/>
-      <c r="K59" s="114"/>
+      <c r="B59" s="52"/>
+      <c r="C59" s="53"/>
+      <c r="D59" s="53"/>
+      <c r="E59" s="53"/>
+      <c r="F59" s="53"/>
+      <c r="G59" s="53"/>
+      <c r="H59" s="53"/>
+      <c r="I59" s="53"/>
+      <c r="J59" s="53"/>
+      <c r="K59" s="54"/>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" s="33"/>
@@ -2345,32 +2345,32 @@
       <c r="K60" s="33"/>
     </row>
     <row r="61" spans="2:11" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="104" t="s">
+      <c r="B61" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="C61" s="104"/>
-      <c r="D61" s="104"/>
-      <c r="E61" s="104"/>
-      <c r="F61" s="104"/>
-      <c r="G61" s="104"/>
-      <c r="H61" s="104"/>
-      <c r="I61" s="104"/>
-      <c r="J61" s="104"/>
-      <c r="K61" s="104"/>
+      <c r="C61" s="56"/>
+      <c r="D61" s="56"/>
+      <c r="E61" s="56"/>
+      <c r="F61" s="56"/>
+      <c r="G61" s="56"/>
+      <c r="H61" s="56"/>
+      <c r="I61" s="56"/>
+      <c r="J61" s="56"/>
+      <c r="K61" s="56"/>
     </row>
     <row r="62" spans="2:11" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="104" t="s">
+      <c r="B62" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="C62" s="104"/>
-      <c r="D62" s="104"/>
-      <c r="E62" s="104"/>
-      <c r="F62" s="104"/>
-      <c r="G62" s="104"/>
-      <c r="H62" s="104"/>
-      <c r="I62" s="104"/>
-      <c r="J62" s="104"/>
-      <c r="K62" s="104"/>
+      <c r="C62" s="56"/>
+      <c r="D62" s="56"/>
+      <c r="E62" s="56"/>
+      <c r="F62" s="56"/>
+      <c r="G62" s="56"/>
+      <c r="H62" s="56"/>
+      <c r="I62" s="56"/>
+      <c r="J62" s="56"/>
+      <c r="K62" s="56"/>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" s="34" t="s">
@@ -2401,149 +2401,149 @@
       <c r="K64" s="34"/>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B65" s="108" t="s">
+      <c r="B65" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="C65" s="108"/>
-      <c r="D65" s="108"/>
-      <c r="E65" s="108"/>
-      <c r="F65" s="108"/>
-      <c r="G65" s="108"/>
-      <c r="H65" s="108"/>
-      <c r="I65" s="108"/>
-      <c r="J65" s="108"/>
-      <c r="K65" s="108"/>
+      <c r="C65" s="48"/>
+      <c r="D65" s="48"/>
+      <c r="E65" s="48"/>
+      <c r="F65" s="48"/>
+      <c r="G65" s="48"/>
+      <c r="H65" s="48"/>
+      <c r="I65" s="48"/>
+      <c r="J65" s="48"/>
+      <c r="K65" s="48"/>
     </row>
     <row r="66" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="108"/>
-      <c r="C66" s="108"/>
-      <c r="D66" s="108"/>
-      <c r="E66" s="108"/>
-      <c r="F66" s="108"/>
-      <c r="G66" s="108"/>
-      <c r="H66" s="108"/>
-      <c r="I66" s="108"/>
-      <c r="J66" s="108"/>
-      <c r="K66" s="108"/>
+      <c r="B66" s="48"/>
+      <c r="C66" s="48"/>
+      <c r="D66" s="48"/>
+      <c r="E66" s="48"/>
+      <c r="F66" s="48"/>
+      <c r="G66" s="48"/>
+      <c r="H66" s="48"/>
+      <c r="I66" s="48"/>
+      <c r="J66" s="48"/>
+      <c r="K66" s="48"/>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H70" s="57"/>
-      <c r="I70" s="57"/>
-      <c r="J70" s="57"/>
+      <c r="H70" s="55"/>
+      <c r="I70" s="55"/>
+      <c r="J70" s="55"/>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B71" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="C71" s="55"/>
+      <c r="D71" s="55"/>
+      <c r="E71" s="55"/>
+      <c r="G71" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="H71" s="55"/>
+      <c r="I71" s="55"/>
+      <c r="J71" s="55"/>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D72" s="34"/>
       <c r="E72" s="34"/>
       <c r="F72" s="34"/>
-      <c r="H72" s="57"/>
-      <c r="I72" s="57"/>
-      <c r="J72" s="57"/>
+      <c r="H72" s="55"/>
+      <c r="I72" s="55"/>
+      <c r="J72" s="55"/>
     </row>
     <row r="73" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="57"/>
-      <c r="C73" s="57"/>
-      <c r="D73" s="57"/>
-      <c r="E73" s="57"/>
-      <c r="G73" s="57"/>
-      <c r="H73" s="57"/>
-      <c r="I73" s="57"/>
-      <c r="J73" s="57"/>
+      <c r="B73" s="55"/>
+      <c r="C73" s="55"/>
+      <c r="D73" s="55"/>
+      <c r="E73" s="55"/>
+      <c r="G73" s="55"/>
+      <c r="H73" s="55"/>
+      <c r="I73" s="55"/>
+      <c r="J73" s="55"/>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B74" s="57" t="s">
-        <v>48</v>
-      </c>
-      <c r="C74" s="57"/>
-      <c r="D74" s="57"/>
-      <c r="E74" s="57"/>
-      <c r="G74" s="57" t="s">
-        <v>49</v>
-      </c>
-      <c r="H74" s="57"/>
-      <c r="I74" s="57"/>
-      <c r="J74" s="57"/>
+      <c r="B74" s="55"/>
+      <c r="C74" s="55"/>
+      <c r="D74" s="55"/>
+      <c r="E74" s="55"/>
+      <c r="G74" s="55"/>
+      <c r="H74" s="55"/>
+      <c r="I74" s="55"/>
+      <c r="J74" s="55"/>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B75" s="57"/>
-      <c r="C75" s="57"/>
-      <c r="D75" s="57"/>
-      <c r="E75" s="57"/>
-      <c r="G75" s="57"/>
-      <c r="H75" s="57"/>
-      <c r="I75" s="57"/>
-      <c r="J75" s="57"/>
+      <c r="B75" s="55"/>
+      <c r="C75" s="55"/>
+      <c r="D75" s="55"/>
+      <c r="E75" s="55"/>
+      <c r="G75" s="55"/>
+      <c r="H75" s="55"/>
+      <c r="I75" s="55"/>
+      <c r="J75" s="55"/>
     </row>
     <row r="78" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A78" s="49" t="s">
+      <c r="A78" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="B78" s="49"/>
-      <c r="C78" s="49"/>
-      <c r="D78" s="49" t="s">
+      <c r="B78" s="46"/>
+      <c r="C78" s="46"/>
+      <c r="D78" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="E78" s="49"/>
-      <c r="F78" s="49"/>
-      <c r="G78" s="49"/>
+      <c r="E78" s="46"/>
+      <c r="F78" s="46"/>
+      <c r="G78" s="46"/>
       <c r="J78" s="38" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="D79" s="107" t="s">
+      <c r="D79" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="E79" s="107"/>
-      <c r="F79" s="107"/>
-      <c r="G79" s="107"/>
+      <c r="E79" s="47"/>
+      <c r="F79" s="47"/>
+      <c r="G79" s="47"/>
       <c r="J79" s="39" t="s">
         <v>40</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="90">
-    <mergeCell ref="D78:G78"/>
-    <mergeCell ref="D79:G79"/>
-    <mergeCell ref="A78:C78"/>
-    <mergeCell ref="B65:K66"/>
-    <mergeCell ref="B56:K59"/>
-    <mergeCell ref="H72:J72"/>
-    <mergeCell ref="H70:J70"/>
-    <mergeCell ref="B75:E75"/>
-    <mergeCell ref="G75:J75"/>
-    <mergeCell ref="B74:E74"/>
-    <mergeCell ref="G74:J74"/>
-    <mergeCell ref="B73:E73"/>
-    <mergeCell ref="G73:J73"/>
-    <mergeCell ref="B62:K62"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="I51:K51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="G52:H52"/>
-    <mergeCell ref="I52:K52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="G53:H53"/>
-    <mergeCell ref="I53:K53"/>
-    <mergeCell ref="B55:K55"/>
-    <mergeCell ref="B61:K61"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="I46:K46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="I47:K47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="I42:K42"/>
+  <mergeCells count="92">
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="B7:K7"/>
+    <mergeCell ref="B8:K8"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="B2:C5"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:K12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:K18"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="B24:C26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I24:K26"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="I30:K30"/>
     <mergeCell ref="B31:C31"/>
@@ -2560,38 +2560,50 @@
     <mergeCell ref="I38:K38"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="B24:C26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="I24:K26"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:K18"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="B7:K7"/>
-    <mergeCell ref="B8:K8"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="B2:C5"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:K12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="I46:K46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="I47:K47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="I53:K53"/>
+    <mergeCell ref="B55:K55"/>
+    <mergeCell ref="B61:K61"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="I51:K51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="I52:K52"/>
+    <mergeCell ref="D78:G78"/>
+    <mergeCell ref="D79:G79"/>
+    <mergeCell ref="A78:C78"/>
+    <mergeCell ref="B65:K66"/>
+    <mergeCell ref="B56:K59"/>
+    <mergeCell ref="H72:J72"/>
+    <mergeCell ref="H70:J70"/>
+    <mergeCell ref="B75:E75"/>
+    <mergeCell ref="G75:J75"/>
+    <mergeCell ref="B74:E74"/>
+    <mergeCell ref="G74:J74"/>
+    <mergeCell ref="B73:E73"/>
+    <mergeCell ref="G73:J73"/>
+    <mergeCell ref="B62:K62"/>
+    <mergeCell ref="B71:E71"/>
+    <mergeCell ref="G71:J71"/>
   </mergeCells>
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.59055118110236227" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
